--- a/ro-crate/ro-crate-metadata.xlsx
+++ b/ro-crate/ro-crate-metadata.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>Name</t>
   </si>
@@ -33,6 +33,9 @@
   </si>
   <si>
     <t>hasPart</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>name</t>
@@ -443,9 +446,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -465,7 +471,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B1" t="s">
         <v>2</v>

--- a/ro-crate/ro-crate-metadata.xlsx
+++ b/ro-crate/ro-crate-metadata.xlsx
@@ -6,13 +6,16 @@
   <sheets>
     <sheet sheetId="1" name="RootDataset" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="@context" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="@type=File" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="@type=SoftwareApplication" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="@type=DigitalFormat" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="201">
   <si>
     <t>Name</t>
   </si>
@@ -32,13 +35,590 @@
     <t>Dataset</t>
   </si>
   <si>
+    <t>pcdm:hasMember</t>
+  </si>
+  <si>
+    <t>["arcp://name,AnonymisingELANFiles", "arcp://name,CollocationAnalyser", "arcp://name,CollocationCalculator", "arcp://name,ConcordanceExplorer", "arcp://name,Concordancer", "arcp://name,Crate-O", "arcp://name,Discursis", "arcp://name,DocumentSimilarity", "arcp://name,ELANAnnotationSplitter", "arcp://name,ELANAudioSegmentation", "arcp://name,ELANCommander", "arcp://name,ELANInventory", "arcp://name,ELANReplacer", "arcp://name,FileRenamer", "arcp://name,ImageDatasetExplorer", "arcp://name,KeywordFinder", "arcp://name,KeywordExtractor", "arcp://name,KeywordsAnalysis", "arcp://name,Lameta", "arcp://name,NetworkVisualiser", "arcp://name,Part-of-SpeechTagger", "arcp://name,POSTagger", "arcp://name,QuotationTool", "arcp://name,SemanticTaggerEnglish", "arcp://name,SentimentExplorer", "arcp://name,TextCleaner", "arcp://name,TopicExplorer", "arcp://name,TopicDetector", "arcp://name,WordFinder", "arcp://name,WordWebber"]</t>
+  </si>
+  <si>
     <t>hasPart</t>
   </si>
   <si>
+    <t>["additional-ro-crate-metadata.xlsx", "images"]</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>contentSize</t>
+  </si>
+  <si>
+    <t>dateModified</t>
+  </si>
+  <si>
+    <t>encodingFormat</t>
+  </si>
+  <si>
+    <t>additional-ro-crate-metadata.xlsx</t>
+  </si>
+  <si>
+    <t>File</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>name</t>
+    <t>2026-08-19T02:08:09Z</t>
+  </si>
+  <si>
+    <t>["https://www.nationalarchives.gov.uk/PRONOM/fmt/214", application/vnd.openxmlformats-officedocument.spreadsheetml.sheet]</t>
+  </si>
+  <si>
+    <t>conformsTo</t>
+  </si>
+  <si>
+    <t>pcdm:memberOf</t>
+  </si>
+  <si>
+    <t>datePublished</t>
+  </si>
+  <si>
+    <t>publisher</t>
+  </si>
+  <si>
+    <t>author</t>
+  </si>
+  <si>
+    <t>programmingLanguage</t>
+  </si>
+  <si>
+    <t>url</t>
+  </si>
+  <si>
+    <t>custom:dataFormat</t>
+  </si>
+  <si>
+    <t>custom:codeURL</t>
+  </si>
+  <si>
+    <t>custom:guideURL</t>
+  </si>
+  <si>
+    <t>creditText</t>
+  </si>
+  <si>
+    <t>custom:additionalNotes</t>
+  </si>
+  <si>
+    <t>arcp://name,AnonymisingELANFiles</t>
+  </si>
+  <si>
+    <t>SoftwareApplication</t>
+  </si>
+  <si>
+    <t>"https://w3id.org/ldac/profile#SoftwareTool"</t>
+  </si>
+  <si>
+    <t>"./"</t>
+  </si>
+  <si>
+    <t>Anonymising ELAN Files</t>
+  </si>
+  <si>
+    <t>Sat Apr 11 2026 00:00:00 GMT+0000 (Coordinated Universal Time)</t>
+  </si>
+  <si>
+    <t>"https://ror.org/019wvm592"</t>
+  </si>
+  <si>
+    <t>"https://orcid.org/0000-0003-4904-2941"</t>
+  </si>
+  <si>
+    <t>Python</t>
+  </si>
+  <si>
+    <t>https://github.com/Supertyp/Anonymising_ELAN_files</t>
+  </si>
+  <si>
+    <t>Anonymise content of ELAN files</t>
+  </si>
+  <si>
+    <t>eaf (ELAN file)</t>
+  </si>
+  <si>
+    <t>arcp://name,CollocationAnalyser</t>
+  </si>
+  <si>
+    <t>Collocation Analyser</t>
+  </si>
+  <si>
+    <t>["https://ror.org/00rqy9422", "https://github.com/SLCLADAL/ladal"]</t>
+  </si>
+  <si>
+    <t>"https://orcid.org/0000-0003-1923-9153"</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>https://ladal.edu.au/tools.html#jupyter-tools</t>
+  </si>
+  <si>
+    <t>Calculates various association measures (collocation statistics) based on textual input and allows you to download the resulting table</t>
+  </si>
+  <si>
+    <t>txt</t>
+  </si>
+  <si>
+    <t>https://ladal.edu.au/tools.html#collocation-analyser</t>
+  </si>
+  <si>
+    <t>arcp://name,CollocationCalculator</t>
+  </si>
+  <si>
+    <t>CollocationCalculator</t>
+  </si>
+  <si>
+    <t>Browser-based</t>
+  </si>
+  <si>
+    <t>https://ladal.edu.au/tools.html#shiny-tools</t>
+  </si>
+  <si>
+    <t>Collocation association measures</t>
+  </si>
+  <si>
+    <t>https://ladal.edu.au/tools.html#collocationcalculator</t>
+  </si>
+  <si>
+    <t>arcp://name,ConcordanceExplorer</t>
+  </si>
+  <si>
+    <t>Concordance Explorer</t>
+  </si>
+  <si>
+    <t>Create Keyword-in-Context displays of words or phrases in a single text or collection of texts and to download the resulting table</t>
+  </si>
+  <si>
+    <t>https://ladal.edu.au/tools.html#concordance-explorer</t>
+  </si>
+  <si>
+    <t>arcp://name,Concordancer</t>
+  </si>
+  <si>
+    <t>Concordancer</t>
+  </si>
+  <si>
+    <t>["https://ror.org/0384j8v12", "https://github.com/Sydney-Informatics-Hub"]</t>
+  </si>
+  <si>
+    <t>"https://orcid.org/0000-0002-3616-6235"</t>
+  </si>
+  <si>
+    <t>https://github.com/Australian-Text-Analytics-Platform/atap_widgets</t>
+  </si>
+  <si>
+    <t>A concordancer that demos how to analyse turn-taking pairs in a concordancer</t>
+  </si>
+  <si>
+    <t>csv, xlsx, plain txt; also zip archive with the supported file formats</t>
+  </si>
+  <si>
+    <t>https://github.com/Australian-Text-Analytics-Platform/atap_widgets/blob/main/docs/concordance_help_pages.pdf</t>
+  </si>
+  <si>
+    <t>Bednarek, M., Mather, M., Maras, K., &amp; Croser, H. (2023). ATAP Concordancer (v0.5.4) [Computer software]. https://github.com/Australian-Text-Analytics-Platform/atap_widgets. DOI. https://doi.org/10.5281/zenodo.10086731</t>
+  </si>
+  <si>
+    <t>arcp://name,Crate-O</t>
+  </si>
+  <si>
+    <t>Crate-O</t>
+  </si>
+  <si>
+    <t>["https://ror.org/00rqy9422", "https://github.com/Language-Research-Technology"]</t>
+  </si>
+  <si>
+    <t>"https://orcid.org/0000-0002-4438-2755"</t>
+  </si>
+  <si>
+    <t>https://github.com/Language-Research-Technology/crate-o</t>
+  </si>
+  <si>
+    <t>Browser-based editor for RO Crates</t>
+  </si>
+  <si>
+    <t>Various - text, video, audio, image, etc.</t>
+  </si>
+  <si>
+    <t>https://www.ldaca.edu.au/resources/user-guides/crate-o/</t>
+  </si>
+  <si>
+    <t>arcp://name,Discursis</t>
+  </si>
+  <si>
+    <t>Discursis</t>
+  </si>
+  <si>
+    <t>https://github.com/Australian-Text-Analytics-Platform/discursis</t>
+  </si>
+  <si>
+    <t>A conversational analysis and visualisation tool</t>
+  </si>
+  <si>
+    <t>csv, xlsx</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/Australian-Text-Analytics-Platform/discursis/master/docs/Discursis%20User%20Guide.pdf</t>
+  </si>
+  <si>
+    <t>Not provided</t>
+  </si>
+  <si>
+    <t>Based on Angus et al</t>
+  </si>
+  <si>
+    <t>arcp://name,DocumentSimilarity</t>
+  </si>
+  <si>
+    <t>Document Similarity</t>
+  </si>
+  <si>
+    <t>["#SonyJufri", "https://orcid.org/0000-0002-1428-2649"]</t>
+  </si>
+  <si>
+    <t>https://github.com/Australian-Text-Analytics-Platform/document-similarity</t>
+  </si>
+  <si>
+    <t>Identifies identical and similar text in a corpus</t>
+  </si>
+  <si>
+    <t>https://github.com/Australian-Text-Analytics-Platform/document-similarity/blob/main/documents/docsim-help-pages.pdf</t>
+  </si>
+  <si>
+    <t>Jufri, Sony &amp; Sun, Chao (2024). Document Similarity. v1.2. Australian Text Analytics Platform. Software. https://github.com/Australian-Text-Analytics-Platform/document-similarity</t>
+  </si>
+  <si>
+    <t>arcp://name,ELANAnnotationSplitter</t>
+  </si>
+  <si>
+    <t>ELAN Annotation Splitter</t>
+  </si>
+  <si>
+    <t>Software program</t>
+  </si>
+  <si>
+    <t>https://github.com/Supertyp/ELAN_apps/</t>
+  </si>
+  <si>
+    <t>Allows to split annotations context depending across a folder full of Elan files. This is a standalone desktop appplication for PC and Mac, not a notebook</t>
+  </si>
+  <si>
+    <t>arcp://name,ELANAudioSegmentation</t>
+  </si>
+  <si>
+    <t>ELAN Audio Segmentation</t>
+  </si>
+  <si>
+    <t>App which takes a audio or video file as imput and creates a ELAN file with empty annotations wherever a voice is heard in the audio</t>
+  </si>
+  <si>
+    <t>wav</t>
+  </si>
+  <si>
+    <t>arcp://name,ELANCommander</t>
+  </si>
+  <si>
+    <t>ELAN Commander</t>
+  </si>
+  <si>
+    <t>https://www.gerlingo.com/ELAN_commander.html</t>
+  </si>
+  <si>
+    <t>Web application to find unwanted characters in annotations</t>
+  </si>
+  <si>
+    <t>arcp://name,ELANInventory</t>
+  </si>
+  <si>
+    <t>ELAN Inventory</t>
+  </si>
+  <si>
+    <t>https://www.gerlingo.com/config_maker.html</t>
+  </si>
+  <si>
+    <t>Web application to access the inventory of a transcription collection and to create config files to load a collection into ANNIS</t>
+  </si>
+  <si>
+    <t>arcp://name,ELANReplacer</t>
+  </si>
+  <si>
+    <t>ELAN Replacer</t>
+  </si>
+  <si>
+    <t>Allows context depending search and replace functionality across a folder full of elan files. Saves hours of manual work for any spelling changes in transcription. This is a stand alone software application for PC and Mac, not a notebook</t>
+  </si>
+  <si>
+    <t>arcp://name,FileRenamer</t>
+  </si>
+  <si>
+    <t>FileRenamer</t>
+  </si>
+  <si>
+    <t>Batch rename plain-text files</t>
+  </si>
+  <si>
+    <t>https://ladal.edu.au/tools.html#filerenamer</t>
+  </si>
+  <si>
+    <t>arcp://name,ImageDatasetExplorer</t>
+  </si>
+  <si>
+    <t>Image Dataset Explorer</t>
+  </si>
+  <si>
+    <t>["https://ror.org/00rqy9422", "https://hass.uq.edu.au/centre-digital-cultures-societies", "https://github.com/Language-Research-Technology"]</t>
+  </si>
+  <si>
+    <t>["https://orcid.org/0009-0008-4603-9521", "https://orcid.org/0000-0002-1824-2361"]</t>
+  </si>
+  <si>
+    <t>https://github.com/Language-Research-Technology/image-dataset-explorer</t>
+  </si>
+  <si>
+    <t>Embeds images from a zip file using off the shelf image embeddings, then creates a static HTML visualisation for browsing/exploring clusters and relations</t>
+  </si>
+  <si>
+    <t>zip archive with jpeg and/or png files</t>
+  </si>
+  <si>
+    <t>arcp://name,KeywordFinder</t>
+  </si>
+  <si>
+    <t>Keyword Finder</t>
+  </si>
+  <si>
+    <t>Calculates various keyness measures describing how words are over or under-represented in the texts you provide, compared to your chosen reference text corpus</t>
+  </si>
+  <si>
+    <t>https://ladal.edu.au/tools.html#keyword-finder</t>
+  </si>
+  <si>
+    <t>arcp://name,KeywordExtractor</t>
+  </si>
+  <si>
+    <t>KeywordExtractor</t>
+  </si>
+  <si>
+    <t>Keyness analysis vs. a reference corpus</t>
+  </si>
+  <si>
+    <t>https://ladal.edu.au/tools.html#keywordextractor</t>
+  </si>
+  <si>
+    <t>arcp://name,KeywordsAnalysis</t>
+  </si>
+  <si>
+    <t>Keywords Analysis</t>
+  </si>
+  <si>
+    <t>https://github.com/Australian-Text-Analytics-Platform/keywords-analysis</t>
+  </si>
+  <si>
+    <t>Tool to analyse words in a collection of corpus and identify whether certain words are over or under-represented in a particular corpus compared to their representation in other corpus</t>
+  </si>
+  <si>
+    <t>https://github.com/Australian-Text-Analytics-Platform/keywords-analysis/blob/main/documents/keywords_help_pages.pdf</t>
+  </si>
+  <si>
+    <t>Jufri, Sony &amp; Sun, Chao (2022). Keywords Analysis. v1.0. Australian Text Analytics Platform. Software. https://github.com/Australian-Text-Analytics-Platform/keywords-analysis</t>
+  </si>
+  <si>
+    <t>arcp://name,Lameta</t>
+  </si>
+  <si>
+    <t>Lameta</t>
+  </si>
+  <si>
+    <t>"https://ror.org/01ej9dk98"</t>
+  </si>
+  <si>
+    <t>["#JohnHatton", "https://orcid.org/0000-0001-8797-1018"]</t>
+  </si>
+  <si>
+    <t>object Object</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lameta is a metadata tool to help with organising collections of files. It is mainly aimed at collections made in the course of documenting language, music, and other cultural expressions.
+Lameta greatly simplifies management of collections and makes the archiving process straightforward and painless for field workers.</t>
+  </si>
+  <si>
+    <t>Various - text, video, audio, image, ELAN annotation (eaf)</t>
+  </si>
+  <si>
+    <t>https://github.com/onset/lameta</t>
+  </si>
+  <si>
+    <t>https://www.elararchive.org/uncategorized/SO_7557c4dd-1c83-485c-b95c-c0a292cfc42c/</t>
+  </si>
+  <si>
+    <t>arcp://name,NetworkVisualiser</t>
+  </si>
+  <si>
+    <t>Network Visualiser</t>
+  </si>
+  <si>
+    <t>Allows you to generate and download network graphs based on your data</t>
+  </si>
+  <si>
+    <t>xlsx</t>
+  </si>
+  <si>
+    <t>https://ladal.edu.au/tools.html#network-visualiser</t>
+  </si>
+  <si>
+    <t>You will need to provide structured data describing the edges and their weights in your network of interest</t>
+  </si>
+  <si>
+    <t>arcp://name,Part-of-SpeechTagger</t>
+  </si>
+  <si>
+    <t>Part-of-Speech Tagger</t>
+  </si>
+  <si>
+    <t>Add part-of-speech tags to texts or collections of texts in more than 60 languages and download the resulting pos-tagged texts</t>
+  </si>
+  <si>
+    <t>https://ladal.edu.au/tools.html#part-of-speech-tagger</t>
+  </si>
+  <si>
+    <t>arcp://name,POSTagger</t>
+  </si>
+  <si>
+    <t>POSTagger</t>
+  </si>
+  <si>
+    <t>Part-of-speech tagging &amp; dependency parsing in 65+ languages</t>
+  </si>
+  <si>
+    <t>https://ladal.edu.au/tools.html#postagger</t>
+  </si>
+  <si>
+    <t>arcp://name,QuotationTool</t>
+  </si>
+  <si>
+    <t>Quotation Tool</t>
+  </si>
+  <si>
+    <t>https://github.com/Australian-Text-Analytics-Platform/quotation-tool</t>
+  </si>
+  <si>
+    <t>A tool to extract quotes and other useful information from a newspaper article/corpus</t>
+  </si>
+  <si>
+    <t>https://github.com/Australian-Text-Analytics-Platform/quotation-tool/blob/main/documents/quotation_help_pages.pdf</t>
+  </si>
+  <si>
+    <t>Jufri, Sony &amp; Sun, Chao (2022). Quotation Tool. v1.0. Australian Text Analytics Platform. Software. https://github.com/Australian-Text-Analytics-Platform/quotation-tool</t>
+  </si>
+  <si>
+    <t>arcp://name,SemanticTaggerEnglish</t>
+  </si>
+  <si>
+    <t>Semantic Tagger (English)</t>
+  </si>
+  <si>
+    <t>https://github.com/Australian-Text-Analytics-Platform/semantic-tagger</t>
+  </si>
+  <si>
+    <t>Used to tag a text/corpus so you can extract token level semantic tags from the tagged texts</t>
+  </si>
+  <si>
+    <t>https://github.com/Australian-Text-Analytics-Platform/semantic-tagger/blob/main/documents/semtag_help_pages.pdf</t>
+  </si>
+  <si>
+    <t>arcp://name,SentimentExplorer</t>
+  </si>
+  <si>
+    <t>SentimentExplorer</t>
+  </si>
+  <si>
+    <t>NRC word-emotion sentiment analysis</t>
+  </si>
+  <si>
+    <t>https://ladal.edu.au/tools.html#sentimentexplorer</t>
+  </si>
+  <si>
+    <t>arcp://name,TextCleaner</t>
+  </si>
+  <si>
+    <t>TextCleaner</t>
+  </si>
+  <si>
+    <t>Remove and replace text elements with regex</t>
+  </si>
+  <si>
+    <t>https://ladal.edu.au/tools.html#textcleaner</t>
+  </si>
+  <si>
+    <t>arcp://name,TopicExplorer</t>
+  </si>
+  <si>
+    <t>Topic Explorer</t>
+  </si>
+  <si>
+    <t>Allows you to generate your own custom topic models using unsupervised and supervised LDA and download the results in an MS Excel spreadsheet</t>
+  </si>
+  <si>
+    <t>https://ladal.edu.au/tools.html#topic-explorer</t>
+  </si>
+  <si>
+    <t>arcp://name,TopicDetector</t>
+  </si>
+  <si>
+    <t>TopicDetector</t>
+  </si>
+  <si>
+    <t>Unsupervised &amp; seeded LDA topic modelling</t>
+  </si>
+  <si>
+    <t>https://ladal.edu.au/tools.html#topicdetector</t>
+  </si>
+  <si>
+    <t>arcp://name,WordFinder</t>
+  </si>
+  <si>
+    <t>WordFinder</t>
+  </si>
+  <si>
+    <t>Keyword-in-context concordancing</t>
+  </si>
+  <si>
+    <t>https://ladal.edu.au/tools.html#wordfinder</t>
+  </si>
+  <si>
+    <t>arcp://name,WordWebber</t>
+  </si>
+  <si>
+    <t>WordWebber</t>
+  </si>
+  <si>
+    <t>Word co-occurrence network visualisation</t>
+  </si>
+  <si>
+    <t>https://ladal.edu.au/tools.html#wordwebber</t>
+  </si>
+  <si>
+    <t>https://www.nationalarchives.gov.uk/PRONOM/fmt/214</t>
+  </si>
+  <si>
+    <t>DigitalFormat</t>
+  </si>
+  <si>
+    <t>Microsoft Excel for Windows</t>
   </si>
 </sst>
 </file>
@@ -415,7 +995,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -452,6 +1032,14 @@
       </c>
       <c r="B4" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -471,10 +1059,1451 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B1" t="s">
         <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="7" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2">
+        <v>16253</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:P31"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="16" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1" t="s">
+        <v>29</v>
+      </c>
+      <c r="O1" t="s">
+        <v>30</v>
+      </c>
+      <c r="P1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L3" t="s">
+        <v>51</v>
+      </c>
+      <c r="M3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" t="s">
+        <v>47</v>
+      </c>
+      <c r="I4" t="s">
+        <v>55</v>
+      </c>
+      <c r="J4" t="s">
+        <v>56</v>
+      </c>
+      <c r="K4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L4" t="s">
+        <v>51</v>
+      </c>
+      <c r="M4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" t="s">
+        <v>47</v>
+      </c>
+      <c r="I5" t="s">
+        <v>48</v>
+      </c>
+      <c r="J5" t="s">
+        <v>49</v>
+      </c>
+      <c r="K5" t="s">
+        <v>61</v>
+      </c>
+      <c r="L5" t="s">
+        <v>51</v>
+      </c>
+      <c r="M5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J6" t="s">
+        <v>67</v>
+      </c>
+      <c r="K6" t="s">
+        <v>68</v>
+      </c>
+      <c r="L6" t="s">
+        <v>69</v>
+      </c>
+      <c r="M6" t="s">
+        <v>67</v>
+      </c>
+      <c r="N6" t="s">
+        <v>70</v>
+      </c>
+      <c r="O6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H7" t="s">
+        <v>75</v>
+      </c>
+      <c r="I7" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K7" t="s">
+        <v>77</v>
+      </c>
+      <c r="L7" t="s">
+        <v>78</v>
+      </c>
+      <c r="M7" t="s">
+        <v>76</v>
+      </c>
+      <c r="N7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" t="s">
+        <v>81</v>
+      </c>
+      <c r="F8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J8" t="s">
+        <v>82</v>
+      </c>
+      <c r="K8" t="s">
+        <v>83</v>
+      </c>
+      <c r="L8" t="s">
+        <v>84</v>
+      </c>
+      <c r="M8" t="s">
+        <v>82</v>
+      </c>
+      <c r="N8" t="s">
+        <v>85</v>
+      </c>
+      <c r="O8" t="s">
+        <v>86</v>
+      </c>
+      <c r="P8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" t="s">
+        <v>89</v>
+      </c>
+      <c r="F9" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" t="s">
+        <v>65</v>
+      </c>
+      <c r="H9" t="s">
+        <v>90</v>
+      </c>
+      <c r="I9" t="s">
+        <v>40</v>
+      </c>
+      <c r="J9" t="s">
+        <v>91</v>
+      </c>
+      <c r="K9" t="s">
+        <v>92</v>
+      </c>
+      <c r="L9" t="s">
+        <v>69</v>
+      </c>
+      <c r="M9" t="s">
+        <v>91</v>
+      </c>
+      <c r="N9" t="s">
+        <v>93</v>
+      </c>
+      <c r="O9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>95</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" t="s">
+        <v>96</v>
+      </c>
+      <c r="F10" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10" t="s">
+        <v>97</v>
+      </c>
+      <c r="J10" t="s">
+        <v>98</v>
+      </c>
+      <c r="K10" t="s">
+        <v>99</v>
+      </c>
+      <c r="L10" t="s">
+        <v>43</v>
+      </c>
+      <c r="M10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>100</v>
+      </c>
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" t="s">
+        <v>101</v>
+      </c>
+      <c r="F11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" t="s">
+        <v>39</v>
+      </c>
+      <c r="I11" t="s">
+        <v>97</v>
+      </c>
+      <c r="J11" t="s">
+        <v>98</v>
+      </c>
+      <c r="K11" t="s">
+        <v>102</v>
+      </c>
+      <c r="L11" t="s">
+        <v>103</v>
+      </c>
+      <c r="M11" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" t="s">
+        <v>105</v>
+      </c>
+      <c r="F12" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12" t="s">
+        <v>39</v>
+      </c>
+      <c r="I12" t="s">
+        <v>55</v>
+      </c>
+      <c r="J12" t="s">
+        <v>106</v>
+      </c>
+      <c r="K12" t="s">
+        <v>107</v>
+      </c>
+      <c r="L12" t="s">
+        <v>43</v>
+      </c>
+      <c r="M12" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" t="s">
+        <v>109</v>
+      </c>
+      <c r="F13" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13" t="s">
+        <v>55</v>
+      </c>
+      <c r="J13" t="s">
+        <v>110</v>
+      </c>
+      <c r="K13" t="s">
+        <v>111</v>
+      </c>
+      <c r="L13" t="s">
+        <v>43</v>
+      </c>
+      <c r="M13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>112</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" t="s">
+        <v>113</v>
+      </c>
+      <c r="F14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" t="s">
+        <v>39</v>
+      </c>
+      <c r="I14" t="s">
+        <v>97</v>
+      </c>
+      <c r="J14" t="s">
+        <v>98</v>
+      </c>
+      <c r="K14" t="s">
+        <v>114</v>
+      </c>
+      <c r="L14" t="s">
+        <v>43</v>
+      </c>
+      <c r="M14" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" t="s">
+        <v>116</v>
+      </c>
+      <c r="F15" t="s">
+        <v>37</v>
+      </c>
+      <c r="G15" t="s">
+        <v>46</v>
+      </c>
+      <c r="H15" t="s">
+        <v>47</v>
+      </c>
+      <c r="I15" t="s">
+        <v>55</v>
+      </c>
+      <c r="J15" t="s">
+        <v>56</v>
+      </c>
+      <c r="K15" t="s">
+        <v>117</v>
+      </c>
+      <c r="L15" t="s">
+        <v>51</v>
+      </c>
+      <c r="M15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>119</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" t="s">
+        <v>120</v>
+      </c>
+      <c r="F16" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" t="s">
+        <v>121</v>
+      </c>
+      <c r="H16" t="s">
+        <v>122</v>
+      </c>
+      <c r="I16" t="s">
+        <v>40</v>
+      </c>
+      <c r="J16" t="s">
+        <v>123</v>
+      </c>
+      <c r="K16" t="s">
+        <v>124</v>
+      </c>
+      <c r="L16" t="s">
+        <v>125</v>
+      </c>
+      <c r="M16" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>126</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" t="s">
+        <v>127</v>
+      </c>
+      <c r="F17" t="s">
+        <v>37</v>
+      </c>
+      <c r="G17" t="s">
+        <v>46</v>
+      </c>
+      <c r="H17" t="s">
+        <v>47</v>
+      </c>
+      <c r="I17" t="s">
+        <v>48</v>
+      </c>
+      <c r="J17" t="s">
+        <v>49</v>
+      </c>
+      <c r="K17" t="s">
+        <v>128</v>
+      </c>
+      <c r="L17" t="s">
+        <v>51</v>
+      </c>
+      <c r="M17" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>130</v>
+      </c>
+      <c r="B18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" t="s">
+        <v>131</v>
+      </c>
+      <c r="F18" t="s">
+        <v>37</v>
+      </c>
+      <c r="G18" t="s">
+        <v>46</v>
+      </c>
+      <c r="H18" t="s">
+        <v>47</v>
+      </c>
+      <c r="I18" t="s">
+        <v>55</v>
+      </c>
+      <c r="J18" t="s">
+        <v>56</v>
+      </c>
+      <c r="K18" t="s">
+        <v>132</v>
+      </c>
+      <c r="L18" t="s">
+        <v>51</v>
+      </c>
+      <c r="M18" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>134</v>
+      </c>
+      <c r="B19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" t="s">
+        <v>135</v>
+      </c>
+      <c r="F19" t="s">
+        <v>37</v>
+      </c>
+      <c r="G19" t="s">
+        <v>65</v>
+      </c>
+      <c r="H19" t="s">
+        <v>90</v>
+      </c>
+      <c r="I19" t="s">
+        <v>40</v>
+      </c>
+      <c r="J19" t="s">
+        <v>136</v>
+      </c>
+      <c r="K19" t="s">
+        <v>137</v>
+      </c>
+      <c r="L19" t="s">
+        <v>69</v>
+      </c>
+      <c r="M19" t="s">
+        <v>136</v>
+      </c>
+      <c r="N19" t="s">
+        <v>138</v>
+      </c>
+      <c r="O19" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>140</v>
+      </c>
+      <c r="B20" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" t="s">
+        <v>35</v>
+      </c>
+      <c r="E20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F20" t="s">
+        <v>37</v>
+      </c>
+      <c r="G20" t="s">
+        <v>142</v>
+      </c>
+      <c r="H20" t="s">
+        <v>143</v>
+      </c>
+      <c r="I20" t="s">
+        <v>97</v>
+      </c>
+      <c r="J20" t="s">
+        <v>144</v>
+      </c>
+      <c r="K20" t="s">
+        <v>145</v>
+      </c>
+      <c r="L20" t="s">
+        <v>146</v>
+      </c>
+      <c r="M20" t="s">
+        <v>147</v>
+      </c>
+      <c r="N20" t="s">
+        <v>148</v>
+      </c>
+      <c r="O20" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>149</v>
+      </c>
+      <c r="B21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C21" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" t="s">
+        <v>150</v>
+      </c>
+      <c r="F21" t="s">
+        <v>37</v>
+      </c>
+      <c r="G21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H21" t="s">
+        <v>47</v>
+      </c>
+      <c r="I21" t="s">
+        <v>48</v>
+      </c>
+      <c r="J21" t="s">
+        <v>49</v>
+      </c>
+      <c r="K21" t="s">
+        <v>151</v>
+      </c>
+      <c r="L21" t="s">
+        <v>152</v>
+      </c>
+      <c r="M21" t="s">
+        <v>153</v>
+      </c>
+      <c r="P21" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>155</v>
+      </c>
+      <c r="B22" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" t="s">
+        <v>156</v>
+      </c>
+      <c r="F22" t="s">
+        <v>37</v>
+      </c>
+      <c r="G22" t="s">
+        <v>46</v>
+      </c>
+      <c r="H22" t="s">
+        <v>47</v>
+      </c>
+      <c r="I22" t="s">
+        <v>48</v>
+      </c>
+      <c r="J22" t="s">
+        <v>49</v>
+      </c>
+      <c r="K22" t="s">
+        <v>157</v>
+      </c>
+      <c r="L22" t="s">
+        <v>51</v>
+      </c>
+      <c r="M22" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>159</v>
+      </c>
+      <c r="B23" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" t="s">
+        <v>160</v>
+      </c>
+      <c r="F23" t="s">
+        <v>37</v>
+      </c>
+      <c r="G23" t="s">
+        <v>46</v>
+      </c>
+      <c r="H23" t="s">
+        <v>47</v>
+      </c>
+      <c r="I23" t="s">
+        <v>55</v>
+      </c>
+      <c r="J23" t="s">
+        <v>56</v>
+      </c>
+      <c r="K23" t="s">
+        <v>161</v>
+      </c>
+      <c r="L23" t="s">
+        <v>51</v>
+      </c>
+      <c r="M23" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>163</v>
+      </c>
+      <c r="B24" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" t="s">
+        <v>164</v>
+      </c>
+      <c r="F24" t="s">
+        <v>37</v>
+      </c>
+      <c r="G24" t="s">
+        <v>65</v>
+      </c>
+      <c r="H24" t="s">
+        <v>90</v>
+      </c>
+      <c r="I24" t="s">
+        <v>40</v>
+      </c>
+      <c r="J24" t="s">
+        <v>165</v>
+      </c>
+      <c r="K24" t="s">
+        <v>166</v>
+      </c>
+      <c r="L24" t="s">
+        <v>69</v>
+      </c>
+      <c r="M24" t="s">
+        <v>165</v>
+      </c>
+      <c r="N24" t="s">
+        <v>167</v>
+      </c>
+      <c r="O24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>169</v>
+      </c>
+      <c r="B25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" t="s">
+        <v>170</v>
+      </c>
+      <c r="F25" t="s">
+        <v>37</v>
+      </c>
+      <c r="G25" t="s">
+        <v>65</v>
+      </c>
+      <c r="H25" t="s">
+        <v>90</v>
+      </c>
+      <c r="I25" t="s">
+        <v>40</v>
+      </c>
+      <c r="J25" t="s">
+        <v>171</v>
+      </c>
+      <c r="K25" t="s">
+        <v>172</v>
+      </c>
+      <c r="L25" t="s">
+        <v>69</v>
+      </c>
+      <c r="M25" t="s">
+        <v>171</v>
+      </c>
+      <c r="N25" t="s">
+        <v>173</v>
+      </c>
+      <c r="O25" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>174</v>
+      </c>
+      <c r="B26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" t="s">
+        <v>175</v>
+      </c>
+      <c r="F26" t="s">
+        <v>37</v>
+      </c>
+      <c r="G26" t="s">
+        <v>46</v>
+      </c>
+      <c r="H26" t="s">
+        <v>47</v>
+      </c>
+      <c r="I26" t="s">
+        <v>55</v>
+      </c>
+      <c r="J26" t="s">
+        <v>56</v>
+      </c>
+      <c r="K26" t="s">
+        <v>176</v>
+      </c>
+      <c r="L26" t="s">
+        <v>51</v>
+      </c>
+      <c r="M26" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>178</v>
+      </c>
+      <c r="B27" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" t="s">
+        <v>34</v>
+      </c>
+      <c r="D27" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" t="s">
+        <v>179</v>
+      </c>
+      <c r="F27" t="s">
+        <v>37</v>
+      </c>
+      <c r="G27" t="s">
+        <v>46</v>
+      </c>
+      <c r="H27" t="s">
+        <v>47</v>
+      </c>
+      <c r="I27" t="s">
+        <v>55</v>
+      </c>
+      <c r="J27" t="s">
+        <v>56</v>
+      </c>
+      <c r="K27" t="s">
+        <v>180</v>
+      </c>
+      <c r="L27" t="s">
+        <v>51</v>
+      </c>
+      <c r="M27" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>182</v>
+      </c>
+      <c r="B28" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" t="s">
+        <v>35</v>
+      </c>
+      <c r="E28" t="s">
+        <v>183</v>
+      </c>
+      <c r="F28" t="s">
+        <v>37</v>
+      </c>
+      <c r="G28" t="s">
+        <v>46</v>
+      </c>
+      <c r="H28" t="s">
+        <v>47</v>
+      </c>
+      <c r="I28" t="s">
+        <v>48</v>
+      </c>
+      <c r="J28" t="s">
+        <v>49</v>
+      </c>
+      <c r="K28" t="s">
+        <v>184</v>
+      </c>
+      <c r="L28" t="s">
+        <v>51</v>
+      </c>
+      <c r="M28" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>186</v>
+      </c>
+      <c r="B29" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" t="s">
+        <v>34</v>
+      </c>
+      <c r="D29" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29" t="s">
+        <v>187</v>
+      </c>
+      <c r="F29" t="s">
+        <v>37</v>
+      </c>
+      <c r="G29" t="s">
+        <v>46</v>
+      </c>
+      <c r="H29" t="s">
+        <v>47</v>
+      </c>
+      <c r="I29" t="s">
+        <v>55</v>
+      </c>
+      <c r="J29" t="s">
+        <v>56</v>
+      </c>
+      <c r="K29" t="s">
+        <v>188</v>
+      </c>
+      <c r="L29" t="s">
+        <v>51</v>
+      </c>
+      <c r="M29" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>190</v>
+      </c>
+      <c r="B30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" t="s">
+        <v>34</v>
+      </c>
+      <c r="D30" t="s">
+        <v>35</v>
+      </c>
+      <c r="E30" t="s">
+        <v>191</v>
+      </c>
+      <c r="F30" t="s">
+        <v>37</v>
+      </c>
+      <c r="G30" t="s">
+        <v>46</v>
+      </c>
+      <c r="H30" t="s">
+        <v>47</v>
+      </c>
+      <c r="I30" t="s">
+        <v>55</v>
+      </c>
+      <c r="J30" t="s">
+        <v>56</v>
+      </c>
+      <c r="K30" t="s">
+        <v>192</v>
+      </c>
+      <c r="L30" t="s">
+        <v>51</v>
+      </c>
+      <c r="M30" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>194</v>
+      </c>
+      <c r="B31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D31" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31" t="s">
+        <v>195</v>
+      </c>
+      <c r="F31" t="s">
+        <v>37</v>
+      </c>
+      <c r="G31" t="s">
+        <v>46</v>
+      </c>
+      <c r="H31" t="s">
+        <v>47</v>
+      </c>
+      <c r="I31" t="s">
+        <v>55</v>
+      </c>
+      <c r="J31" t="s">
+        <v>56</v>
+      </c>
+      <c r="K31" t="s">
+        <v>196</v>
+      </c>
+      <c r="L31" t="s">
+        <v>152</v>
+      </c>
+      <c r="M31" t="s">
+        <v>197</v>
+      </c>
+      <c r="P31" t="s">
+        <v>154</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="3" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C2" t="s">
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/ro-crate/ro-crate-metadata.xlsx
+++ b/ro-crate/ro-crate-metadata.xlsx
@@ -12,14 +12,13 @@
     <sheet sheetId="6" name="@type=ldac_DataReuseLicense" state="visible" r:id="rId9"/>
     <sheet sheetId="7" name="@type=SoftwareApplication" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="@type=RepositoryCollection" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="@type=DigitalFormat" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="299">
   <si>
     <t>Name</t>
   </si>
@@ -60,7 +59,7 @@
     <t>datePublished</t>
   </si>
   <si>
-    <t>Sat Apr 11 2026 00:00:00 GMT+0000 (Coordinated Universal Time)</t>
+    <t>Sat Apr 11 2026 10:00:00 GMT+1000 (Australian Eastern Standard Time)</t>
   </si>
   <si>
     <t>inLanguage</t>
@@ -99,7 +98,7 @@
     <t>hasPart</t>
   </si>
   <si>
-    <t>["additional-ro-crate-metadata.xlsx", "images"]</t>
+    <t>"images"</t>
   </si>
   <si>
     <t>ldac</t>
@@ -114,229 +113,214 @@
     <t>arcp://name,custom/terms#</t>
   </si>
   <si>
-    <t>contentSize</t>
-  </si>
-  <si>
-    <t>dateModified</t>
+    <t>test_file.jpg</t>
+  </si>
+  <si>
+    <t>File</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0000-0002-1428-2649</t>
+  </si>
+  <si>
+    <t>Person</t>
+  </si>
+  <si>
+    <t>Chao Sun</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0009-0008-4603-9521</t>
+  </si>
+  <si>
+    <t>Jasper Chong</t>
+  </si>
+  <si>
+    <t>#JohnHatton</t>
+  </si>
+  <si>
+    <t>John Hatton</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0000-0002-3616-6235</t>
+  </si>
+  <si>
+    <t>Marius Mather</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0000-0003-1923-9153</t>
+  </si>
+  <si>
+    <t>Martin Schweinberger</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0000-0002-4438-2755</t>
+  </si>
+  <si>
+    <t>Moises Sacal Bonequi</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0000-0001-8797-1018</t>
+  </si>
+  <si>
+    <t>Nick Thieberger</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0000-0003-2933-6627</t>
+  </si>
+  <si>
+    <t>Robert Fleet</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0000-0002-1824-2361</t>
+  </si>
+  <si>
+    <t>Sam Hames</t>
+  </si>
+  <si>
+    <t>#SonyJufri</t>
+  </si>
+  <si>
+    <t>Sony Jufri</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0000-0003-4904-2941</t>
+  </si>
+  <si>
+    <t>Wolfgang Barth</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0000-0002-2118-3147</t>
+  </si>
+  <si>
+    <t>River Tae Smith</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0009-0006-2241-3377</t>
+  </si>
+  <si>
+    <t>Rosanna Smith</t>
+  </si>
+  <si>
+    <t>https://orcid.org/0000-0003-3237-9943</t>
+  </si>
+  <si>
+    <t>Simon Musgrave</t>
+  </si>
+  <si>
+    <t>https://github.com/Language-Research-Technology</t>
+  </si>
+  <si>
+    <t>Organization</t>
+  </si>
+  <si>
+    <t>Language Data Commons of Australia</t>
+  </si>
+  <si>
+    <t>https://ror.org/00rqy9422</t>
+  </si>
+  <si>
+    <t>The University of Queensland</t>
+  </si>
+  <si>
+    <t>https://ror.org/019wvm592</t>
+  </si>
+  <si>
+    <t>Australian National University</t>
+  </si>
+  <si>
+    <t>https://ror.org/01ej9dk98</t>
+  </si>
+  <si>
+    <t>The University of Melbourne</t>
+  </si>
+  <si>
+    <t>https://ror.org/0384j8v12</t>
+  </si>
+  <si>
+    <t>The University of Sydney</t>
+  </si>
+  <si>
+    <t>https://ror.org/03pnv4752</t>
+  </si>
+  <si>
+    <t>Queensland University of Technology</t>
+  </si>
+  <si>
+    <t>https://github.com/Sydney-Informatics-Hub</t>
+  </si>
+  <si>
+    <t>Sydney Informatics Hub</t>
+  </si>
+  <si>
+    <t>https://github.com/QUT-Digital-Observatory</t>
+  </si>
+  <si>
+    <t>Digital Observatory</t>
+  </si>
+  <si>
+    <t>https://github.com/SLCLADAL/ladal</t>
+  </si>
+  <si>
+    <t>Language Technology and Data Analysis Laboratory</t>
+  </si>
+  <si>
+    <t>https://hass.uq.edu.au/centre-digital-cultures-societies</t>
+  </si>
+  <si>
+    <t>Centre for Digital Cultures &amp; Societies</t>
+  </si>
+  <si>
+    <t>ldac:allowTextIndex</t>
+  </si>
+  <si>
+    <t>isPartOf</t>
+  </si>
+  <si>
+    <t>https://creativecommons.org/licenses/by/4.0/</t>
+  </si>
+  <si>
+    <t>ldac:DataReuseLicense</t>
+  </si>
+  <si>
+    <t>Attribution 4.0 International (CC BY 4.0)</t>
+  </si>
+  <si>
+    <t>You are free to: Share — copy and redistribute the material in any medium or format. Adapt — remix, transform, and build upon the material for any purpose, even commercially. This license is acceptable for Free Cultural Works. The licensor cannot revoke these freedoms as long as you follow the license terms.</t>
+  </si>
+  <si>
+    <t>"./"</t>
+  </si>
+  <si>
+    <t>conformsTo</t>
+  </si>
+  <si>
+    <t>pcdm:memberOf</t>
+  </si>
+  <si>
+    <t>programmingLanguage</t>
+  </si>
+  <si>
+    <t>url</t>
+  </si>
+  <si>
+    <t>custom:dataFormat</t>
+  </si>
+  <si>
+    <t>custom:codeURL</t>
+  </si>
+  <si>
+    <t>custom:guideURL</t>
+  </si>
+  <si>
+    <t>creditText</t>
+  </si>
+  <si>
+    <t>custom:additionalNotes</t>
+  </si>
+  <si>
+    <t>input</t>
   </si>
   <si>
     <t>encodingFormat</t>
-  </si>
-  <si>
-    <t>test_file.jpg</t>
-  </si>
-  <si>
-    <t>File</t>
-  </si>
-  <si>
-    <t>additional-ro-crate-metadata.xlsx</t>
-  </si>
-  <si>
-    <t>2026-08-19T02:36:29Z</t>
-  </si>
-  <si>
-    <t>["https://www.nationalarchives.gov.uk/PRONOM/fmt/214", application/vnd.openxmlformats-officedocument.spreadsheetml.sheet]</t>
-  </si>
-  <si>
-    <t>https://orcid.org/0000-0002-1428-2649</t>
-  </si>
-  <si>
-    <t>Person</t>
-  </si>
-  <si>
-    <t>Chao Sun</t>
-  </si>
-  <si>
-    <t>https://orcid.org/0009-0008-4603-9521</t>
-  </si>
-  <si>
-    <t>Jasper Chong</t>
-  </si>
-  <si>
-    <t>#JohnHatton</t>
-  </si>
-  <si>
-    <t>John Hatton</t>
-  </si>
-  <si>
-    <t>https://orcid.org/0000-0002-3616-6235</t>
-  </si>
-  <si>
-    <t>Marius Mather</t>
-  </si>
-  <si>
-    <t>https://orcid.org/0000-0003-1923-9153</t>
-  </si>
-  <si>
-    <t>Martin Schweinberger</t>
-  </si>
-  <si>
-    <t>https://orcid.org/0000-0002-4438-2755</t>
-  </si>
-  <si>
-    <t>Moises Sacal Bonequi</t>
-  </si>
-  <si>
-    <t>https://orcid.org/0000-0001-8797-1018</t>
-  </si>
-  <si>
-    <t>Nick Thieberger</t>
-  </si>
-  <si>
-    <t>https://orcid.org/0000-0003-2933-6627</t>
-  </si>
-  <si>
-    <t>Robert Fleet</t>
-  </si>
-  <si>
-    <t>https://orcid.org/0000-0002-1824-2361</t>
-  </si>
-  <si>
-    <t>Sam Hames</t>
-  </si>
-  <si>
-    <t>#SonyJufri</t>
-  </si>
-  <si>
-    <t>Sony Jufri</t>
-  </si>
-  <si>
-    <t>https://orcid.org/0000-0003-4904-2941</t>
-  </si>
-  <si>
-    <t>Wolfgang Barth</t>
-  </si>
-  <si>
-    <t>https://orcid.org/0000-0002-2118-3147</t>
-  </si>
-  <si>
-    <t>River Tae Smith</t>
-  </si>
-  <si>
-    <t>https://orcid.org/0009-0006-2241-3377</t>
-  </si>
-  <si>
-    <t>Rosanna Smith</t>
-  </si>
-  <si>
-    <t>https://orcid.org/0000-0003-3237-9943</t>
-  </si>
-  <si>
-    <t>Simon Musgrave</t>
-  </si>
-  <si>
-    <t>https://github.com/Language-Research-Technology</t>
-  </si>
-  <si>
-    <t>Organization</t>
-  </si>
-  <si>
-    <t>Language Data Commons of Australia</t>
-  </si>
-  <si>
-    <t>https://ror.org/00rqy9422</t>
-  </si>
-  <si>
-    <t>The University of Queensland</t>
-  </si>
-  <si>
-    <t>https://ror.org/019wvm592</t>
-  </si>
-  <si>
-    <t>Australian National University</t>
-  </si>
-  <si>
-    <t>https://ror.org/01ej9dk98</t>
-  </si>
-  <si>
-    <t>The University of Melbourne</t>
-  </si>
-  <si>
-    <t>https://ror.org/0384j8v12</t>
-  </si>
-  <si>
-    <t>The University of Sydney</t>
-  </si>
-  <si>
-    <t>https://ror.org/03pnv4752</t>
-  </si>
-  <si>
-    <t>Queensland University of Technology</t>
-  </si>
-  <si>
-    <t>https://github.com/Sydney-Informatics-Hub</t>
-  </si>
-  <si>
-    <t>Sydney Informatics Hub</t>
-  </si>
-  <si>
-    <t>https://github.com/QUT-Digital-Observatory</t>
-  </si>
-  <si>
-    <t>Digital Observatory</t>
-  </si>
-  <si>
-    <t>https://github.com/SLCLADAL/ladal</t>
-  </si>
-  <si>
-    <t>Language Technology and Data Analysis Laboratory</t>
-  </si>
-  <si>
-    <t>https://hass.uq.edu.au/centre-digital-cultures-societies</t>
-  </si>
-  <si>
-    <t>Centre for Digital Cultures &amp; Societies</t>
-  </si>
-  <si>
-    <t>ldac:allowTextIndex</t>
-  </si>
-  <si>
-    <t>isPartOf</t>
-  </si>
-  <si>
-    <t>https://creativecommons.org/licenses/by/4.0/</t>
-  </si>
-  <si>
-    <t>ldac:DataReuseLicense</t>
-  </si>
-  <si>
-    <t>Attribution 4.0 International (CC BY 4.0)</t>
-  </si>
-  <si>
-    <t>You are free to: Share — copy and redistribute the material in any medium or format. Adapt — remix, transform, and build upon the material for any purpose, even commercially. This license is acceptable for Free Cultural Works. The licensor cannot revoke these freedoms as long as you follow the license terms.</t>
-  </si>
-  <si>
-    <t>"./"</t>
-  </si>
-  <si>
-    <t>conformsTo</t>
-  </si>
-  <si>
-    <t>pcdm:memberOf</t>
-  </si>
-  <si>
-    <t>programmingLanguage</t>
-  </si>
-  <si>
-    <t>url</t>
-  </si>
-  <si>
-    <t>custom:dataFormat</t>
-  </si>
-  <si>
-    <t>custom:codeURL</t>
-  </si>
-  <si>
-    <t>custom:guideURL</t>
-  </si>
-  <si>
-    <t>creditText</t>
-  </si>
-  <si>
-    <t>custom:additionalNotes</t>
-  </si>
-  <si>
-    <t>input</t>
   </si>
   <si>
     <t>arcp://name,AnonymisingELANFiles</t>
@@ -859,7 +843,7 @@
     <t>Farms to freeways notebook</t>
   </si>
   <si>
-    <t>Sun Jul 07 2024 00:00:00 GMT+0000 (Coordinated Universal Time)</t>
+    <t>Sun Jul 07 2024 10:00:00 GMT+1000 (Australian Eastern Standard Time)</t>
   </si>
   <si>
     <t>"Mel Mistica"</t>
@@ -932,15 +916,6 @@
   </si>
   <si>
     <t>Australian Twittersphere (AuTS) aggregated data - Collection</t>
-  </si>
-  <si>
-    <t>https://www.nationalarchives.gov.uk/PRONOM/fmt/214</t>
-  </si>
-  <si>
-    <t>DigitalFormat</t>
-  </si>
-  <si>
-    <t>Microsoft Excel for Windows</t>
   </si>
 </sst>
 </file>
@@ -1483,64 +1458,26 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="7" width="20" customWidth="1"/>
+    <col min="1" max="2" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
       <c r="B1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3">
-        <v>16253</v>
-      </c>
-      <c r="F3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1570,156 +1507,156 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C13" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1749,112 +1686,112 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1885,30 +1822,30 @@
         <v>8</v>
       </c>
       <c r="E1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="F1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1933,10 +1870,10 @@
         <v>4</v>
       </c>
       <c r="C1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D1" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E1" t="s">
         <v>6</v>
@@ -1951,1494 +1888,1494 @@
         <v>17</v>
       </c>
       <c r="I1" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="J1" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="K1" t="s">
         <v>8</v>
       </c>
       <c r="L1" t="s">
+        <v>94</v>
+      </c>
+      <c r="M1" t="s">
+        <v>95</v>
+      </c>
+      <c r="N1" t="s">
+        <v>96</v>
+      </c>
+      <c r="O1" t="s">
+        <v>97</v>
+      </c>
+      <c r="P1" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>99</v>
+      </c>
+      <c r="R1" t="s">
         <v>100</v>
-      </c>
-      <c r="M1" t="s">
-        <v>101</v>
-      </c>
-      <c r="N1" t="s">
-        <v>102</v>
-      </c>
-      <c r="O1" t="s">
-        <v>103</v>
-      </c>
-      <c r="P1" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>105</v>
-      </c>
-      <c r="R1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F2" t="s">
         <v>13</v>
       </c>
       <c r="G2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H2" t="s">
+        <v>106</v>
+      </c>
+      <c r="I2" t="s">
+        <v>107</v>
+      </c>
+      <c r="J2" t="s">
+        <v>108</v>
+      </c>
+      <c r="K2" t="s">
+        <v>109</v>
+      </c>
+      <c r="L2" t="s">
         <v>110</v>
       </c>
-      <c r="H2" t="s">
-        <v>111</v>
-      </c>
-      <c r="I2" t="s">
-        <v>112</v>
-      </c>
-      <c r="J2" t="s">
-        <v>113</v>
-      </c>
-      <c r="K2" t="s">
-        <v>114</v>
-      </c>
-      <c r="L2" t="s">
-        <v>115</v>
-      </c>
       <c r="M2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D3" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="F3" t="s">
         <v>13</v>
       </c>
       <c r="G3" t="s">
+        <v>113</v>
+      </c>
+      <c r="H3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I3" t="s">
+        <v>115</v>
+      </c>
+      <c r="J3" t="s">
+        <v>116</v>
+      </c>
+      <c r="K3" t="s">
+        <v>117</v>
+      </c>
+      <c r="L3" t="s">
         <v>118</v>
       </c>
-      <c r="H3" t="s">
+      <c r="M3" t="s">
         <v>119</v>
-      </c>
-      <c r="I3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J3" t="s">
-        <v>121</v>
-      </c>
-      <c r="K3" t="s">
-        <v>122</v>
-      </c>
-      <c r="L3" t="s">
-        <v>123</v>
-      </c>
-      <c r="M3" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B4" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E4" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
       </c>
       <c r="G4" t="s">
+        <v>113</v>
+      </c>
+      <c r="H4" t="s">
+        <v>114</v>
+      </c>
+      <c r="I4" t="s">
+        <v>122</v>
+      </c>
+      <c r="J4" t="s">
+        <v>123</v>
+      </c>
+      <c r="K4" t="s">
+        <v>124</v>
+      </c>
+      <c r="L4" t="s">
         <v>118</v>
       </c>
-      <c r="H4" t="s">
-        <v>119</v>
-      </c>
-      <c r="I4" t="s">
-        <v>127</v>
-      </c>
-      <c r="J4" t="s">
-        <v>128</v>
-      </c>
-      <c r="K4" t="s">
-        <v>129</v>
-      </c>
-      <c r="L4" t="s">
-        <v>123</v>
-      </c>
       <c r="M4" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B5" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C5" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E5" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
       </c>
       <c r="G5" t="s">
+        <v>113</v>
+      </c>
+      <c r="H5" t="s">
+        <v>114</v>
+      </c>
+      <c r="I5" t="s">
+        <v>115</v>
+      </c>
+      <c r="J5" t="s">
+        <v>116</v>
+      </c>
+      <c r="K5" t="s">
+        <v>128</v>
+      </c>
+      <c r="L5" t="s">
         <v>118</v>
       </c>
-      <c r="H5" t="s">
-        <v>119</v>
-      </c>
-      <c r="I5" t="s">
-        <v>120</v>
-      </c>
-      <c r="J5" t="s">
-        <v>121</v>
-      </c>
-      <c r="K5" t="s">
-        <v>133</v>
-      </c>
-      <c r="L5" t="s">
-        <v>123</v>
-      </c>
       <c r="M5" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B6" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C6" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
       </c>
       <c r="G6" t="s">
+        <v>132</v>
+      </c>
+      <c r="H6" t="s">
+        <v>133</v>
+      </c>
+      <c r="I6" t="s">
+        <v>107</v>
+      </c>
+      <c r="J6" t="s">
+        <v>134</v>
+      </c>
+      <c r="K6" t="s">
+        <v>135</v>
+      </c>
+      <c r="L6" t="s">
+        <v>136</v>
+      </c>
+      <c r="M6" t="s">
+        <v>134</v>
+      </c>
+      <c r="N6" t="s">
         <v>137</v>
       </c>
-      <c r="H6" t="s">
+      <c r="O6" t="s">
         <v>138</v>
-      </c>
-      <c r="I6" t="s">
-        <v>112</v>
-      </c>
-      <c r="J6" t="s">
-        <v>139</v>
-      </c>
-      <c r="K6" t="s">
-        <v>140</v>
-      </c>
-      <c r="L6" t="s">
-        <v>141</v>
-      </c>
-      <c r="M6" t="s">
-        <v>139</v>
-      </c>
-      <c r="N6" t="s">
-        <v>142</v>
-      </c>
-      <c r="O6" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="B7" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C7" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E7" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="F7" t="s">
         <v>13</v>
       </c>
       <c r="G7" t="s">
+        <v>141</v>
+      </c>
+      <c r="H7" t="s">
+        <v>142</v>
+      </c>
+      <c r="I7" t="s">
+        <v>122</v>
+      </c>
+      <c r="J7" t="s">
+        <v>143</v>
+      </c>
+      <c r="K7" t="s">
+        <v>144</v>
+      </c>
+      <c r="L7" t="s">
+        <v>145</v>
+      </c>
+      <c r="M7" t="s">
+        <v>143</v>
+      </c>
+      <c r="N7" t="s">
         <v>146</v>
-      </c>
-      <c r="H7" t="s">
-        <v>147</v>
-      </c>
-      <c r="I7" t="s">
-        <v>127</v>
-      </c>
-      <c r="J7" t="s">
-        <v>148</v>
-      </c>
-      <c r="K7" t="s">
-        <v>149</v>
-      </c>
-      <c r="L7" t="s">
-        <v>150</v>
-      </c>
-      <c r="M7" t="s">
-        <v>148</v>
-      </c>
-      <c r="N7" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C8" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="I8" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="J8" t="s">
+        <v>149</v>
+      </c>
+      <c r="K8" t="s">
+        <v>150</v>
+      </c>
+      <c r="L8" t="s">
+        <v>151</v>
+      </c>
+      <c r="M8" t="s">
+        <v>149</v>
+      </c>
+      <c r="N8" t="s">
+        <v>152</v>
+      </c>
+      <c r="O8" t="s">
+        <v>153</v>
+      </c>
+      <c r="P8" t="s">
         <v>154</v>
-      </c>
-      <c r="K8" t="s">
-        <v>155</v>
-      </c>
-      <c r="L8" t="s">
-        <v>156</v>
-      </c>
-      <c r="M8" t="s">
-        <v>154</v>
-      </c>
-      <c r="N8" t="s">
-        <v>157</v>
-      </c>
-      <c r="O8" t="s">
-        <v>158</v>
-      </c>
-      <c r="P8" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B9" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E9" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F9" t="s">
         <v>13</v>
       </c>
       <c r="G9" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="H9" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I9" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="J9" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="K9" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="L9" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="M9" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="N9" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="O9" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B10" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C10" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E10" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="F10" t="s">
         <v>13</v>
       </c>
       <c r="G10" t="s">
+        <v>105</v>
+      </c>
+      <c r="H10" t="s">
+        <v>106</v>
+      </c>
+      <c r="I10" t="s">
+        <v>164</v>
+      </c>
+      <c r="J10" t="s">
+        <v>165</v>
+      </c>
+      <c r="K10" t="s">
+        <v>166</v>
+      </c>
+      <c r="L10" t="s">
         <v>110</v>
       </c>
-      <c r="H10" t="s">
-        <v>111</v>
-      </c>
-      <c r="I10" t="s">
-        <v>169</v>
-      </c>
-      <c r="J10" t="s">
-        <v>170</v>
-      </c>
-      <c r="K10" t="s">
-        <v>171</v>
-      </c>
-      <c r="L10" t="s">
-        <v>115</v>
-      </c>
       <c r="M10" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B11" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C11" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E11" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="H11" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="I11" t="s">
+        <v>164</v>
+      </c>
+      <c r="J11" t="s">
+        <v>165</v>
+      </c>
+      <c r="K11" t="s">
         <v>169</v>
       </c>
-      <c r="J11" t="s">
+      <c r="L11" t="s">
         <v>170</v>
       </c>
-      <c r="K11" t="s">
-        <v>174</v>
-      </c>
-      <c r="L11" t="s">
-        <v>175</v>
-      </c>
       <c r="M11" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B12" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E12" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
       </c>
       <c r="G12" t="s">
+        <v>105</v>
+      </c>
+      <c r="H12" t="s">
+        <v>106</v>
+      </c>
+      <c r="I12" t="s">
+        <v>122</v>
+      </c>
+      <c r="J12" t="s">
+        <v>173</v>
+      </c>
+      <c r="K12" t="s">
+        <v>174</v>
+      </c>
+      <c r="L12" t="s">
         <v>110</v>
       </c>
-      <c r="H12" t="s">
-        <v>111</v>
-      </c>
-      <c r="I12" t="s">
-        <v>127</v>
-      </c>
-      <c r="J12" t="s">
-        <v>178</v>
-      </c>
-      <c r="K12" t="s">
-        <v>179</v>
-      </c>
-      <c r="L12" t="s">
-        <v>115</v>
-      </c>
       <c r="M12" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B13" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C13" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E13" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="F13" t="s">
         <v>13</v>
       </c>
       <c r="G13" t="s">
+        <v>105</v>
+      </c>
+      <c r="H13" t="s">
+        <v>106</v>
+      </c>
+      <c r="I13" t="s">
+        <v>122</v>
+      </c>
+      <c r="J13" t="s">
+        <v>177</v>
+      </c>
+      <c r="K13" t="s">
+        <v>178</v>
+      </c>
+      <c r="L13" t="s">
         <v>110</v>
       </c>
-      <c r="H13" t="s">
-        <v>111</v>
-      </c>
-      <c r="I13" t="s">
-        <v>127</v>
-      </c>
-      <c r="J13" t="s">
-        <v>182</v>
-      </c>
-      <c r="K13" t="s">
-        <v>183</v>
-      </c>
-      <c r="L13" t="s">
-        <v>115</v>
-      </c>
       <c r="M13" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="B14" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C14" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D14" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E14" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
       </c>
       <c r="G14" t="s">
+        <v>105</v>
+      </c>
+      <c r="H14" t="s">
+        <v>106</v>
+      </c>
+      <c r="I14" t="s">
+        <v>164</v>
+      </c>
+      <c r="J14" t="s">
+        <v>165</v>
+      </c>
+      <c r="K14" t="s">
+        <v>181</v>
+      </c>
+      <c r="L14" t="s">
         <v>110</v>
       </c>
-      <c r="H14" t="s">
-        <v>111</v>
-      </c>
-      <c r="I14" t="s">
-        <v>169</v>
-      </c>
-      <c r="J14" t="s">
-        <v>170</v>
-      </c>
-      <c r="K14" t="s">
-        <v>186</v>
-      </c>
-      <c r="L14" t="s">
-        <v>115</v>
-      </c>
       <c r="M14" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B15" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C15" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E15" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
       </c>
       <c r="G15" t="s">
+        <v>113</v>
+      </c>
+      <c r="H15" t="s">
+        <v>114</v>
+      </c>
+      <c r="I15" t="s">
+        <v>122</v>
+      </c>
+      <c r="J15" t="s">
+        <v>123</v>
+      </c>
+      <c r="K15" t="s">
+        <v>184</v>
+      </c>
+      <c r="L15" t="s">
         <v>118</v>
       </c>
-      <c r="H15" t="s">
-        <v>119</v>
-      </c>
-      <c r="I15" t="s">
-        <v>127</v>
-      </c>
-      <c r="J15" t="s">
-        <v>128</v>
-      </c>
-      <c r="K15" t="s">
-        <v>189</v>
-      </c>
-      <c r="L15" t="s">
-        <v>123</v>
-      </c>
       <c r="M15" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B16" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C16" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D16" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E16" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="H16" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="I16" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="J16" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="K16" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="L16" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="M16" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C17" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D17" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E17" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="F17" t="s">
         <v>13</v>
       </c>
       <c r="G17" t="s">
+        <v>113</v>
+      </c>
+      <c r="H17" t="s">
+        <v>114</v>
+      </c>
+      <c r="I17" t="s">
+        <v>115</v>
+      </c>
+      <c r="J17" t="s">
+        <v>116</v>
+      </c>
+      <c r="K17" t="s">
+        <v>195</v>
+      </c>
+      <c r="L17" t="s">
         <v>118</v>
       </c>
-      <c r="H17" t="s">
-        <v>119</v>
-      </c>
-      <c r="I17" t="s">
-        <v>120</v>
-      </c>
-      <c r="J17" t="s">
-        <v>121</v>
-      </c>
-      <c r="K17" t="s">
-        <v>200</v>
-      </c>
-      <c r="L17" t="s">
-        <v>123</v>
-      </c>
       <c r="M17" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C18" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E18" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="F18" t="s">
         <v>13</v>
       </c>
       <c r="G18" t="s">
+        <v>113</v>
+      </c>
+      <c r="H18" t="s">
+        <v>114</v>
+      </c>
+      <c r="I18" t="s">
+        <v>122</v>
+      </c>
+      <c r="J18" t="s">
+        <v>123</v>
+      </c>
+      <c r="K18" t="s">
+        <v>199</v>
+      </c>
+      <c r="L18" t="s">
         <v>118</v>
       </c>
-      <c r="H18" t="s">
-        <v>119</v>
-      </c>
-      <c r="I18" t="s">
-        <v>127</v>
-      </c>
-      <c r="J18" t="s">
-        <v>128</v>
-      </c>
-      <c r="K18" t="s">
-        <v>204</v>
-      </c>
-      <c r="L18" t="s">
-        <v>123</v>
-      </c>
       <c r="M18" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B19" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D19" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E19" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="F19" t="s">
         <v>13</v>
       </c>
       <c r="G19" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="H19" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I19" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="J19" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="K19" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="L19" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="M19" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="N19" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="O19" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C20" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D20" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E20" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="F20" t="s">
         <v>13</v>
       </c>
       <c r="G20" t="s">
+        <v>209</v>
+      </c>
+      <c r="H20" t="s">
+        <v>210</v>
+      </c>
+      <c r="I20" t="s">
+        <v>164</v>
+      </c>
+      <c r="J20" t="s">
+        <v>211</v>
+      </c>
+      <c r="K20" t="s">
+        <v>212</v>
+      </c>
+      <c r="L20" t="s">
+        <v>213</v>
+      </c>
+      <c r="M20" t="s">
         <v>214</v>
       </c>
-      <c r="H20" t="s">
+      <c r="N20" t="s">
         <v>215</v>
       </c>
-      <c r="I20" t="s">
-        <v>169</v>
-      </c>
-      <c r="J20" t="s">
-        <v>216</v>
-      </c>
-      <c r="K20" t="s">
-        <v>217</v>
-      </c>
-      <c r="L20" t="s">
-        <v>218</v>
-      </c>
-      <c r="M20" t="s">
-        <v>219</v>
-      </c>
-      <c r="N20" t="s">
-        <v>220</v>
-      </c>
       <c r="O20" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B21" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C21" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D21" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E21" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F21" t="s">
         <v>13</v>
       </c>
       <c r="G21" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="H21" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="I21" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="J21" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="K21" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="L21" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="M21" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="P21" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B22" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C22" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E22" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="F22" t="s">
         <v>13</v>
       </c>
       <c r="G22" t="s">
+        <v>113</v>
+      </c>
+      <c r="H22" t="s">
+        <v>114</v>
+      </c>
+      <c r="I22" t="s">
+        <v>115</v>
+      </c>
+      <c r="J22" t="s">
+        <v>116</v>
+      </c>
+      <c r="K22" t="s">
+        <v>224</v>
+      </c>
+      <c r="L22" t="s">
         <v>118</v>
       </c>
-      <c r="H22" t="s">
-        <v>119</v>
-      </c>
-      <c r="I22" t="s">
-        <v>120</v>
-      </c>
-      <c r="J22" t="s">
-        <v>121</v>
-      </c>
-      <c r="K22" t="s">
-        <v>229</v>
-      </c>
-      <c r="L22" t="s">
-        <v>123</v>
-      </c>
       <c r="M22" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B23" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C23" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D23" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E23" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="F23" t="s">
         <v>13</v>
       </c>
       <c r="G23" t="s">
+        <v>113</v>
+      </c>
+      <c r="H23" t="s">
+        <v>114</v>
+      </c>
+      <c r="I23" t="s">
+        <v>122</v>
+      </c>
+      <c r="J23" t="s">
+        <v>123</v>
+      </c>
+      <c r="K23" t="s">
+        <v>228</v>
+      </c>
+      <c r="L23" t="s">
         <v>118</v>
       </c>
-      <c r="H23" t="s">
-        <v>119</v>
-      </c>
-      <c r="I23" t="s">
-        <v>127</v>
-      </c>
-      <c r="J23" t="s">
-        <v>128</v>
-      </c>
-      <c r="K23" t="s">
-        <v>233</v>
-      </c>
-      <c r="L23" t="s">
-        <v>123</v>
-      </c>
       <c r="M23" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B24" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C24" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D24" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E24" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="F24" t="s">
         <v>13</v>
       </c>
       <c r="G24" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="H24" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I24" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="J24" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="K24" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="L24" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="M24" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="N24" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="O24" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B25" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C25" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D25" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E25" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="F25" t="s">
         <v>13</v>
       </c>
       <c r="G25" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="H25" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I25" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="J25" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="K25" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="L25" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="M25" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="N25" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="O25" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="B26" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C26" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D26" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E26" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="F26" t="s">
         <v>13</v>
       </c>
       <c r="G26" t="s">
+        <v>113</v>
+      </c>
+      <c r="H26" t="s">
+        <v>114</v>
+      </c>
+      <c r="I26" t="s">
+        <v>122</v>
+      </c>
+      <c r="J26" t="s">
+        <v>123</v>
+      </c>
+      <c r="K26" t="s">
+        <v>243</v>
+      </c>
+      <c r="L26" t="s">
         <v>118</v>
       </c>
-      <c r="H26" t="s">
-        <v>119</v>
-      </c>
-      <c r="I26" t="s">
-        <v>127</v>
-      </c>
-      <c r="J26" t="s">
-        <v>128</v>
-      </c>
-      <c r="K26" t="s">
-        <v>248</v>
-      </c>
-      <c r="L26" t="s">
-        <v>123</v>
-      </c>
       <c r="M26" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="B27" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C27" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D27" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E27" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="F27" t="s">
         <v>13</v>
       </c>
       <c r="G27" t="s">
+        <v>113</v>
+      </c>
+      <c r="H27" t="s">
+        <v>114</v>
+      </c>
+      <c r="I27" t="s">
+        <v>122</v>
+      </c>
+      <c r="J27" t="s">
+        <v>123</v>
+      </c>
+      <c r="K27" t="s">
+        <v>247</v>
+      </c>
+      <c r="L27" t="s">
         <v>118</v>
       </c>
-      <c r="H27" t="s">
-        <v>119</v>
-      </c>
-      <c r="I27" t="s">
-        <v>127</v>
-      </c>
-      <c r="J27" t="s">
-        <v>128</v>
-      </c>
-      <c r="K27" t="s">
-        <v>252</v>
-      </c>
-      <c r="L27" t="s">
-        <v>123</v>
-      </c>
       <c r="M27" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="B28" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C28" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D28" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E28" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="F28" t="s">
         <v>13</v>
       </c>
       <c r="G28" t="s">
+        <v>113</v>
+      </c>
+      <c r="H28" t="s">
+        <v>114</v>
+      </c>
+      <c r="I28" t="s">
+        <v>115</v>
+      </c>
+      <c r="J28" t="s">
+        <v>116</v>
+      </c>
+      <c r="K28" t="s">
+        <v>251</v>
+      </c>
+      <c r="L28" t="s">
         <v>118</v>
       </c>
-      <c r="H28" t="s">
-        <v>119</v>
-      </c>
-      <c r="I28" t="s">
-        <v>120</v>
-      </c>
-      <c r="J28" t="s">
-        <v>121</v>
-      </c>
-      <c r="K28" t="s">
-        <v>256</v>
-      </c>
-      <c r="L28" t="s">
-        <v>123</v>
-      </c>
       <c r="M28" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="B29" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C29" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D29" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E29" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="F29" t="s">
         <v>13</v>
       </c>
       <c r="G29" t="s">
+        <v>113</v>
+      </c>
+      <c r="H29" t="s">
+        <v>114</v>
+      </c>
+      <c r="I29" t="s">
+        <v>122</v>
+      </c>
+      <c r="J29" t="s">
+        <v>123</v>
+      </c>
+      <c r="K29" t="s">
+        <v>255</v>
+      </c>
+      <c r="L29" t="s">
         <v>118</v>
       </c>
-      <c r="H29" t="s">
-        <v>119</v>
-      </c>
-      <c r="I29" t="s">
-        <v>127</v>
-      </c>
-      <c r="J29" t="s">
-        <v>128</v>
-      </c>
-      <c r="K29" t="s">
-        <v>260</v>
-      </c>
-      <c r="L29" t="s">
-        <v>123</v>
-      </c>
       <c r="M29" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B30" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C30" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D30" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E30" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="F30" t="s">
         <v>13</v>
       </c>
       <c r="G30" t="s">
+        <v>113</v>
+      </c>
+      <c r="H30" t="s">
+        <v>114</v>
+      </c>
+      <c r="I30" t="s">
+        <v>122</v>
+      </c>
+      <c r="J30" t="s">
+        <v>123</v>
+      </c>
+      <c r="K30" t="s">
+        <v>259</v>
+      </c>
+      <c r="L30" t="s">
         <v>118</v>
       </c>
-      <c r="H30" t="s">
-        <v>119</v>
-      </c>
-      <c r="I30" t="s">
-        <v>127</v>
-      </c>
-      <c r="J30" t="s">
-        <v>128</v>
-      </c>
-      <c r="K30" t="s">
-        <v>264</v>
-      </c>
-      <c r="L30" t="s">
-        <v>123</v>
-      </c>
       <c r="M30" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="B31" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C31" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D31" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E31" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="F31" t="s">
         <v>13</v>
       </c>
       <c r="G31" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="H31" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="I31" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="J31" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="K31" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="L31" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="M31" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="P31" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B32" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C32" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="D32" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E32" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="F32" t="s">
         <v>13</v>
       </c>
       <c r="G32" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="H32" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="I32" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="J32" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="K32" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="M32" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="Q32" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="R32" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>272</v>
+      </c>
+      <c r="B33" t="s">
+        <v>102</v>
+      </c>
+      <c r="C33" t="s">
+        <v>265</v>
+      </c>
+      <c r="D33" t="s">
+        <v>89</v>
+      </c>
+      <c r="E33" t="s">
+        <v>273</v>
+      </c>
+      <c r="F33" t="s">
+        <v>274</v>
+      </c>
+      <c r="G33" t="s">
+        <v>105</v>
+      </c>
+      <c r="H33" t="s">
+        <v>275</v>
+      </c>
+      <c r="I33" t="s">
+        <v>107</v>
+      </c>
+      <c r="J33" t="s">
+        <v>272</v>
+      </c>
+      <c r="L33" t="s">
+        <v>276</v>
+      </c>
+      <c r="M33" t="s">
+        <v>272</v>
+      </c>
+      <c r="Q33" t="s">
         <v>277</v>
       </c>
-      <c r="B33" t="s">
-        <v>107</v>
-      </c>
-      <c r="C33" t="s">
-        <v>270</v>
-      </c>
-      <c r="D33" t="s">
-        <v>95</v>
-      </c>
-      <c r="E33" t="s">
-        <v>278</v>
-      </c>
-      <c r="F33" t="s">
-        <v>279</v>
-      </c>
-      <c r="G33" t="s">
-        <v>110</v>
-      </c>
-      <c r="H33" t="s">
-        <v>280</v>
-      </c>
-      <c r="I33" t="s">
-        <v>112</v>
-      </c>
-      <c r="J33" t="s">
-        <v>277</v>
-      </c>
-      <c r="L33" t="s">
-        <v>281</v>
-      </c>
-      <c r="M33" t="s">
-        <v>277</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>282</v>
-      </c>
       <c r="R33" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>278</v>
+      </c>
+      <c r="B34" t="s">
+        <v>102</v>
+      </c>
+      <c r="C34" t="s">
+        <v>265</v>
+      </c>
+      <c r="D34" t="s">
+        <v>89</v>
+      </c>
+      <c r="E34" t="s">
+        <v>279</v>
+      </c>
+      <c r="G34" t="s">
+        <v>280</v>
+      </c>
+      <c r="H34" t="s">
+        <v>281</v>
+      </c>
+      <c r="I34" t="s">
+        <v>107</v>
+      </c>
+      <c r="J34" t="s">
+        <v>278</v>
+      </c>
+      <c r="K34" t="s">
+        <v>282</v>
+      </c>
+      <c r="L34" t="s">
         <v>283</v>
       </c>
-      <c r="B34" t="s">
-        <v>107</v>
-      </c>
-      <c r="C34" t="s">
-        <v>270</v>
-      </c>
-      <c r="D34" t="s">
-        <v>95</v>
-      </c>
-      <c r="E34" t="s">
+      <c r="M34" t="s">
         <v>284</v>
       </c>
-      <c r="G34" t="s">
+      <c r="Q34" t="s">
         <v>285</v>
       </c>
-      <c r="H34" t="s">
-        <v>286</v>
-      </c>
-      <c r="I34" t="s">
-        <v>112</v>
-      </c>
-      <c r="J34" t="s">
-        <v>283</v>
-      </c>
-      <c r="K34" t="s">
-        <v>287</v>
-      </c>
-      <c r="L34" t="s">
-        <v>288</v>
-      </c>
-      <c r="M34" t="s">
-        <v>289</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>290</v>
-      </c>
       <c r="R34" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B35" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C35" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="D35" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E35" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="F35" t="s">
         <v>13</v>
       </c>
       <c r="G35" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="H35" t="s">
+        <v>281</v>
+      </c>
+      <c r="I35" t="s">
+        <v>107</v>
+      </c>
+      <c r="J35" t="s">
         <v>286</v>
       </c>
-      <c r="I35" t="s">
-        <v>112</v>
-      </c>
-      <c r="J35" t="s">
-        <v>291</v>
-      </c>
       <c r="K35" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="L35" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="M35" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="Q35" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="R35" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -3468,82 +3405,46 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B2" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C2" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="B3" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="C3" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B4" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C4" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B5" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C5" t="s">
-        <v>298</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="3" width="20" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>304</v>
-      </c>
-      <c r="B2" t="s">
-        <v>305</v>
-      </c>
-      <c r="C2" t="s">
-        <v>306</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>

--- a/ro-crate/ro-crate-metadata.xlsx
+++ b/ro-crate/ro-crate-metadata.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="304">
   <si>
     <t>Name</t>
   </si>
@@ -59,7 +59,7 @@
     <t>datePublished</t>
   </si>
   <si>
-    <t>Sat Apr 11 2026 10:00:00 GMT+1000 (Australian Eastern Standard Time)</t>
+    <t>Sat Apr 11 2026 00:00:00 GMT+0000 (Coordinated Universal Time)</t>
   </si>
   <si>
     <t>inLanguage</t>
@@ -92,7 +92,7 @@
     <t>pcdm:hasMember</t>
   </si>
   <si>
-    <t>["arcp://name,AnonymisingELANFiles", "arcp://name,CollocationAnalyser", "arcp://name,CollocationCalculator", "arcp://name,ConcordanceExplorer", "arcp://name,Concordancer", "arcp://name,Crate-O", "arcp://name,Discursis", "arcp://name,DocumentSimilarity", "arcp://name,ELANAnnotationSplitter", "arcp://name,ELANAudioSegmentation", "arcp://name,ELANCommander", "arcp://name,ELANInventory", "arcp://name,ELANReplacer", "arcp://name,FileRenamer", "arcp://name,ImageDatasetExplorer", "arcp://name,KeywordFinder", "arcp://name,KeywordExtractor", "arcp://name,KeywordsAnalysis", "arcp://name,Lameta", "arcp://name,NetworkVisualiser", "arcp://name,Part-of-SpeechTagger", "arcp://name,POSTagger", "arcp://name,QuotationTool", "arcp://name,SemanticTaggerEnglish", "arcp://name,SentimentExplorer", "arcp://name,TextCleaner", "arcp://name,TopicExplorer", "arcp://name,TopicDetector", "arcp://name,WordFinder", "arcp://name,WordWebber", "https://github.com/Supertyp/Anonymising_ELAN_files", "https://github.com/Australian-Text-Analytics-Platform/farms-to-freeways", "https://data.ldaca.edu.au/object?_id=https%3A%2F%2Fgithub.com%2FAustralian-Text-Analytics-Platform%2Fnotebook-ausreddit%2Fblob%2Fmain%2Fexploration.ipynb", "https://data.ldaca.edu.au/object?_id=https%3A%2F%2Fgithub.com%2FAustralian-Text-Analytics-Platform%2Fnotebook-twittersphere%2Fblob%2Fmain%2Fexploration.ipynb"]</t>
+    <t>["arcp://name,AnonymisingELANFiles", "arcp://name,CollocationAnalyser", "arcp://name,CollocationCalculator", "arcp://name,ConcordanceExplorer", "arcp://name,Concordancer", "arcp://name,Crate-O", "arcp://name,Discursis", "arcp://name,DocumentSimilarity", "arcp://name,ELANAnnotationSplitter", "arcp://name,ELANAudioSegmentation", "arcp://name,ELANCommander", "arcp://name,ELANInventory", "arcp://name,ELANReplacer", "arcp://name,FileRenamer", "arcp://name,ImageDatasetExplorer", "arcp://name,KeywordFinder", "arcp://name,KeywordExtractor", "arcp://name,KeywordsAnalysis", "arcp://name,Lameta", "arcp://name,NetworkVisualiser", "arcp://name,Part-of-SpeechTagger", "arcp://name,POSTagger", "arcp://name,QuotationTool", "arcp://name,SemanticTaggerEnglish", "arcp://name,SentimentExplorer", "arcp://name,TextCleaner", "arcp://name,TopicExplorer", "arcp://name,TopicDetector", "arcp://name,WordFinder", "arcp://name,WordWebber", "https://data.ldaca.edu.au/object?_id=https://github.com/Australian-Text-Analytics-Platform/cooee/blob/main/cooee.ipynb", "https://github.com/Australian-Text-Analytics-Platform/farms-to-freeways", "https://data.ldaca.edu.au/object?_id=https%3A%2F%2Fgithub.com%2FAustralian-Text-Analytics-Platform%2Fnotebook-ausreddit%2Fblob%2Fmain%2Fexploration.ipynb", "https://data.ldaca.edu.au/object?_id=https%3A%2F%2Fgithub.com%2FAustralian-Text-Analytics-Platform%2Fnotebook-twittersphere%2Fblob%2Fmain%2Fexploration.ipynb"]</t>
   </si>
   <si>
     <t>hasPart</t>
@@ -113,12 +113,69 @@
     <t>arcp://name,custom/terms#</t>
   </si>
   <si>
-    <t>test_file.jpg</t>
+    <t>isPartOf</t>
+  </si>
+  <si>
+    <t>images/collocation-calculator.png</t>
   </si>
   <si>
     <t>File</t>
   </si>
   <si>
+    <t>"./"</t>
+  </si>
+  <si>
+    <t>images/concordancer.png</t>
+  </si>
+  <si>
+    <t>images/crate-o.png</t>
+  </si>
+  <si>
+    <t>images/discursis.png</t>
+  </si>
+  <si>
+    <t>images/document-similarity.png</t>
+  </si>
+  <si>
+    <t>images/file-renamer.png</t>
+  </si>
+  <si>
+    <t>images/image-dataset-explorer.png</t>
+  </si>
+  <si>
+    <t>images/keyword-analysis.png</t>
+  </si>
+  <si>
+    <t>images/keyword-extractor.png</t>
+  </si>
+  <si>
+    <t>images/lameta.png</t>
+  </si>
+  <si>
+    <t>images/pos-tagger.png</t>
+  </si>
+  <si>
+    <t>images/quotation-tool.png</t>
+  </si>
+  <si>
+    <t>images/semantic-tagger.png</t>
+  </si>
+  <si>
+    <t>images/sentiment-explorer.png</t>
+  </si>
+  <si>
+    <t>images/text-cleaner.png</t>
+  </si>
+  <si>
+    <t>images/topic-detector.png</t>
+  </si>
+  <si>
+    <t>images/word-finder.png</t>
+  </si>
+  <si>
+    <t>images/word-webber.png</t>
+  </si>
+  <si>
     <t>https://orcid.org/0000-0002-1428-2649</t>
   </si>
   <si>
@@ -272,9 +329,6 @@
     <t>ldac:allowTextIndex</t>
   </si>
   <si>
-    <t>isPartOf</t>
-  </si>
-  <si>
     <t>https://creativecommons.org/licenses/by/4.0/</t>
   </si>
   <si>
@@ -287,9 +341,6 @@
     <t>You are free to: Share — copy and redistribute the material in any medium or format. Adapt — remix, transform, and build upon the material for any purpose, even commercially. This license is acceptable for Free Cultural Works. The licensor cannot revoke these freedoms as long as you follow the license terms.</t>
   </si>
   <si>
-    <t>"./"</t>
-  </si>
-  <si>
     <t>conformsTo</t>
   </si>
   <si>
@@ -308,6 +359,9 @@
     <t>custom:codeURL</t>
   </si>
   <si>
+    <t>image</t>
+  </si>
+  <si>
     <t>custom:guideURL</t>
   </si>
   <si>
@@ -377,9 +431,6 @@
     <t>txt</t>
   </si>
   <si>
-    <t>https://ladal.edu.au/tools.html#collocation-analyser</t>
-  </si>
-  <si>
     <t>arcp://name,CollocationCalculator</t>
   </si>
   <si>
@@ -395,9 +446,6 @@
     <t>Collocation association measures</t>
   </si>
   <si>
-    <t>https://ladal.edu.au/tools.html#collocationcalculator</t>
-  </si>
-  <si>
     <t>arcp://name,ConcordanceExplorer</t>
   </si>
   <si>
@@ -407,9 +455,6 @@
     <t>Create Keyword-in-Context displays of words or phrases in a single text or collection of texts and to download the resulting table</t>
   </si>
   <si>
-    <t>https://ladal.edu.au/tools.html#concordance-explorer</t>
-  </si>
-  <si>
     <t>arcp://name,Concordancer</t>
   </si>
   <si>
@@ -575,9 +620,6 @@
     <t>Batch rename plain-text files</t>
   </si>
   <si>
-    <t>https://ladal.edu.au/tools.html#filerenamer</t>
-  </si>
-  <si>
     <t>arcp://name,ImageDatasetExplorer</t>
   </si>
   <si>
@@ -608,9 +650,6 @@
     <t>Calculates various keyness measures describing how words are over or under-represented in the texts you provide, compared to your chosen reference text corpus</t>
   </si>
   <si>
-    <t>https://ladal.edu.au/tools.html#keyword-finder</t>
-  </si>
-  <si>
     <t>arcp://name,KeywordExtractor</t>
   </si>
   <si>
@@ -620,9 +659,6 @@
     <t>Keyness analysis vs. a reference corpus</t>
   </si>
   <si>
-    <t>https://ladal.edu.au/tools.html#keywordextractor</t>
-  </si>
-  <si>
     <t>arcp://name,KeywordsAnalysis</t>
   </si>
   <si>
@@ -653,7 +689,7 @@
     <t>["#JohnHatton", "https://orcid.org/0000-0001-8797-1018"]</t>
   </si>
   <si>
-    <t>object Object</t>
+    <t>https://lameta.org</t>
   </si>
   <si>
     <t xml:space="preserve">Lameta is a metadata tool to help with organising collections of files. It is mainly aimed at collections made in the course of documenting language, music, and other cultural expressions.
@@ -669,6 +705,9 @@
     <t>https://www.elararchive.org/uncategorized/SO_7557c4dd-1c83-485c-b95c-c0a292cfc42c/</t>
   </si>
   <si>
+    <t>object Object</t>
+  </si>
+  <si>
     <t>arcp://name,NetworkVisualiser</t>
   </si>
   <si>
@@ -681,9 +720,6 @@
     <t>xlsx</t>
   </si>
   <si>
-    <t>https://ladal.edu.au/tools.html#network-visualiser</t>
-  </si>
-  <si>
     <t>You will need to provide structured data describing the edges and their weights in your network of interest</t>
   </si>
   <si>
@@ -696,9 +732,6 @@
     <t>Add part-of-speech tags to texts or collections of texts in more than 60 languages and download the resulting pos-tagged texts</t>
   </si>
   <si>
-    <t>https://ladal.edu.au/tools.html#part-of-speech-tagger</t>
-  </si>
-  <si>
     <t>arcp://name,POSTagger</t>
   </si>
   <si>
@@ -708,9 +741,6 @@
     <t>Part-of-speech tagging &amp; dependency parsing in 65+ languages</t>
   </si>
   <si>
-    <t>https://ladal.edu.au/tools.html#postagger</t>
-  </si>
-  <si>
     <t>arcp://name,QuotationTool</t>
   </si>
   <si>
@@ -753,9 +783,6 @@
     <t>NRC word-emotion sentiment analysis</t>
   </si>
   <si>
-    <t>https://ladal.edu.au/tools.html#sentimentexplorer</t>
-  </si>
-  <si>
     <t>arcp://name,TextCleaner</t>
   </si>
   <si>
@@ -765,9 +792,6 @@
     <t>Remove and replace text elements with regex</t>
   </si>
   <si>
-    <t>https://ladal.edu.au/tools.html#textcleaner</t>
-  </si>
-  <si>
     <t>arcp://name,TopicExplorer</t>
   </si>
   <si>
@@ -777,9 +801,6 @@
     <t>Allows you to generate your own custom topic models using unsupervised and supervised LDA and download the results in an MS Excel spreadsheet</t>
   </si>
   <si>
-    <t>https://ladal.edu.au/tools.html#topic-explorer</t>
-  </si>
-  <si>
     <t>arcp://name,TopicDetector</t>
   </si>
   <si>
@@ -789,9 +810,6 @@
     <t>Unsupervised &amp; seeded LDA topic modelling</t>
   </si>
   <si>
-    <t>https://ladal.edu.au/tools.html#topicdetector</t>
-  </si>
-  <si>
     <t>arcp://name,WordFinder</t>
   </si>
   <si>
@@ -801,9 +819,6 @@
     <t>Keyword-in-context concordancing</t>
   </si>
   <si>
-    <t>https://ladal.edu.au/tools.html#wordfinder</t>
-  </si>
-  <si>
     <t>arcp://name,WordWebber</t>
   </si>
   <si>
@@ -813,7 +828,7 @@
     <t>Word co-occurrence network visualisation</t>
   </si>
   <si>
-    <t>https://ladal.edu.au/tools.html#wordwebber</t>
+    <t>https://data.ldaca.edu.au/object?_id=https://github.com/Australian-Text-Analytics-Platform/cooee/blob/main/cooee.ipynb</t>
   </si>
   <si>
     <t>["https://w3id.org/ldac/profile#SoftwareTool", "object Object"]</t>
@@ -843,7 +858,7 @@
     <t>Farms to freeways notebook</t>
   </si>
   <si>
-    <t>Sun Jul 07 2024 10:00:00 GMT+1000 (Australian Eastern Standard Time)</t>
+    <t>Sun Jul 07 2024 00:00:00 GMT+0000 (Coordinated Universal Time)</t>
   </si>
   <si>
     <t>"Mel Mistica"</t>
@@ -1458,26 +1473,219 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="20" customWidth="1"/>
+    <col min="1" max="3" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
       <c r="B1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1507,156 +1715,156 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="C14" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -1686,112 +1894,112 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="C2" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1822,30 +2030,30 @@
         <v>8</v>
       </c>
       <c r="E1" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="F1" t="s">
-        <v>84</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1856,13 +2064,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R35"/>
+  <dimension ref="A1:S35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="18" width="20" customWidth="1"/>
+    <col min="1" max="19" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -1870,10 +2078,10 @@
         <v>4</v>
       </c>
       <c r="C1" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="D1" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="E1" t="s">
         <v>6</v>
@@ -1888,1494 +2096,1497 @@
         <v>17</v>
       </c>
       <c r="I1" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="J1" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="K1" t="s">
         <v>8</v>
       </c>
       <c r="L1" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="M1" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="N1" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="O1" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="P1" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="Q1" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="R1" t="s">
-        <v>100</v>
+        <v>117</v>
+      </c>
+      <c r="S1" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="F2" t="s">
         <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="H2" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="I2" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="J2" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="K2" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="L2" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="M2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="B3" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="F3" t="s">
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="H3" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="I3" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="J3" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="K3" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="L3" t="s">
-        <v>118</v>
-      </c>
-      <c r="M3" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B4" t="s">
         <v>120</v>
       </c>
-      <c r="B4" t="s">
-        <v>102</v>
-      </c>
       <c r="C4" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D4" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="H4" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="I4" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="J4" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="K4" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="L4" t="s">
-        <v>118</v>
-      </c>
-      <c r="M4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="N4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="H5" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="I5" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="J5" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="K5" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="L5" t="s">
-        <v>118</v>
-      </c>
-      <c r="M5" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="B6" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D6" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="H6" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="I6" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="J6" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="K6" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="L6" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="M6" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="N6" t="s">
-        <v>137</v>
+        <v>35</v>
       </c>
       <c r="O6" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+      <c r="P6" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="B7" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E7" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="F7" t="s">
         <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="H7" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="I7" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="J7" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="K7" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="L7" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="M7" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="N7" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+      <c r="O7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="B8" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E8" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="I8" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="J8" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="K8" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="L8" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="M8" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="N8" t="s">
-        <v>152</v>
+        <v>37</v>
       </c>
       <c r="O8" t="s">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="P8" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="B9" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E9" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="F9" t="s">
         <v>13</v>
       </c>
       <c r="G9" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="H9" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I9" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="J9" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="K9" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="L9" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="M9" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="N9" t="s">
-        <v>160</v>
+        <v>38</v>
       </c>
       <c r="O9" t="s">
-        <v>161</v>
+        <v>175</v>
+      </c>
+      <c r="P9" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="B10" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D10" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="F10" t="s">
         <v>13</v>
       </c>
       <c r="G10" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="H10" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="I10" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="J10" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="K10" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="L10" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="M10" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="B11" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E11" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="H11" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="I11" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="J11" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="K11" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="L11" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="M11" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="B12" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="H12" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="I12" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="J12" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="K12" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="L12" t="s">
-        <v>110</v>
-      </c>
-      <c r="M12" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="B13" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E13" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="F13" t="s">
         <v>13</v>
       </c>
       <c r="G13" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="H13" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="I13" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="J13" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="K13" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="L13" t="s">
-        <v>110</v>
-      </c>
-      <c r="M13" t="s">
-        <v>177</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="B14" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D14" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="H14" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="I14" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="J14" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="K14" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="L14" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="M14" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="B15" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D15" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E15" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
       </c>
       <c r="G15" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="H15" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="I15" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="J15" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="K15" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="L15" t="s">
-        <v>118</v>
-      </c>
-      <c r="M15" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="N15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="B16" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D16" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E16" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="H16" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="I16" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="J16" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="K16" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="L16" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="M16" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+      <c r="N16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="B17" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D17" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E17" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="F17" t="s">
         <v>13</v>
       </c>
       <c r="G17" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="H17" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="I17" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="J17" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="K17" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="L17" t="s">
-        <v>118</v>
-      </c>
-      <c r="M17" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D18" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="F18" t="s">
         <v>13</v>
       </c>
       <c r="G18" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="H18" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="I18" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="J18" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="K18" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="L18" t="s">
-        <v>118</v>
-      </c>
-      <c r="M18" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="N18" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="B19" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C19" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D19" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E19" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="F19" t="s">
         <v>13</v>
       </c>
       <c r="G19" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="H19" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I19" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="J19" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="K19" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="L19" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="M19" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="N19" t="s">
-        <v>205</v>
+        <v>41</v>
       </c>
       <c r="O19" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+      <c r="P19" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="B20" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D20" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E20" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="F20" t="s">
         <v>13</v>
       </c>
       <c r="G20" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="H20" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="I20" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="J20" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="K20" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="L20" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="M20" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="N20" t="s">
-        <v>215</v>
+        <v>43</v>
       </c>
       <c r="O20" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+      <c r="P20" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="B21" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C21" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D21" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E21" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="F21" t="s">
         <v>13</v>
       </c>
       <c r="G21" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="H21" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="I21" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="J21" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="K21" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="L21" t="s">
-        <v>219</v>
-      </c>
-      <c r="M21" t="s">
-        <v>220</v>
-      </c>
-      <c r="P21" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="B22" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D22" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E22" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="F22" t="s">
         <v>13</v>
       </c>
       <c r="G22" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="H22" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="I22" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="J22" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="K22" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="L22" t="s">
-        <v>118</v>
-      </c>
-      <c r="M22" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="B23" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D23" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E23" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="F23" t="s">
         <v>13</v>
       </c>
       <c r="G23" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="H23" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="I23" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="J23" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="K23" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="L23" t="s">
-        <v>118</v>
-      </c>
-      <c r="M23" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="N23" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="B24" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D24" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E24" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="F24" t="s">
         <v>13</v>
       </c>
       <c r="G24" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="H24" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I24" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="J24" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="K24" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="L24" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="M24" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="N24" t="s">
-        <v>234</v>
+        <v>45</v>
       </c>
       <c r="O24" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+        <v>244</v>
+      </c>
+      <c r="P24" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="B25" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C25" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D25" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E25" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="F25" t="s">
         <v>13</v>
       </c>
       <c r="G25" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="H25" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="I25" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="J25" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="K25" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="L25" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="M25" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="N25" t="s">
-        <v>240</v>
+        <v>46</v>
       </c>
       <c r="O25" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+      <c r="P25" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="B26" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D26" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E26" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="F26" t="s">
         <v>13</v>
       </c>
       <c r="G26" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="H26" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="I26" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="J26" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="K26" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="L26" t="s">
-        <v>118</v>
-      </c>
-      <c r="M26" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="B27" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C27" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D27" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E27" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="F27" t="s">
         <v>13</v>
       </c>
       <c r="G27" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="H27" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="I27" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="J27" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="K27" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="L27" t="s">
-        <v>118</v>
-      </c>
-      <c r="M27" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="N27" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="B28" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C28" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D28" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E28" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="F28" t="s">
         <v>13</v>
       </c>
       <c r="G28" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="H28" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="I28" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="J28" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="K28" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="L28" t="s">
-        <v>118</v>
-      </c>
-      <c r="M28" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="B29" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C29" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D29" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E29" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="F29" t="s">
         <v>13</v>
       </c>
       <c r="G29" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="H29" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="I29" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="J29" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="K29" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="L29" t="s">
-        <v>118</v>
-      </c>
-      <c r="M29" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="N29" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B30" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C30" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D30" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E30" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="F30" t="s">
         <v>13</v>
       </c>
       <c r="G30" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="H30" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="I30" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="J30" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="K30" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="L30" t="s">
-        <v>118</v>
-      </c>
-      <c r="M30" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+      <c r="N30" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B31" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C31" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="D31" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E31" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="F31" t="s">
         <v>13</v>
       </c>
       <c r="G31" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="H31" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="I31" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="J31" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="K31" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="L31" t="s">
-        <v>219</v>
-      </c>
-      <c r="M31" t="s">
-        <v>264</v>
-      </c>
-      <c r="P31" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+      <c r="N31" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>108</v>
+        <v>269</v>
       </c>
       <c r="B32" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C32" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D32" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E32" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F32" t="s">
         <v>13</v>
       </c>
       <c r="G32" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="H32" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="I32" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="J32" t="s">
-        <v>108</v>
+        <v>269</v>
       </c>
       <c r="K32" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="M32" t="s">
-        <v>269</v>
-      </c>
-      <c r="Q32" t="s">
+        <v>274</v>
+      </c>
+      <c r="R32" t="s">
+        <v>275</v>
+      </c>
+      <c r="S32" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>277</v>
+      </c>
+      <c r="B33" t="s">
+        <v>120</v>
+      </c>
+      <c r="C33" t="s">
         <v>270</v>
       </c>
-      <c r="R32" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>272</v>
-      </c>
-      <c r="B33" t="s">
-        <v>102</v>
-      </c>
-      <c r="C33" t="s">
-        <v>265</v>
-      </c>
       <c r="D33" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E33" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="F33" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="G33" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="H33" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="I33" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="J33" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="L33" t="s">
+        <v>281</v>
+      </c>
+      <c r="M33" t="s">
+        <v>277</v>
+      </c>
+      <c r="R33" t="s">
+        <v>282</v>
+      </c>
+      <c r="S33" t="s">
         <v>276</v>
       </c>
-      <c r="M33" t="s">
-        <v>272</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>277</v>
-      </c>
-      <c r="R33" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B34" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C34" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D34" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E34" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="G34" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="H34" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="I34" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="J34" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="K34" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="L34" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="M34" t="s">
-        <v>284</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="R34" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+        <v>290</v>
+      </c>
+      <c r="S34" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B35" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C35" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D35" t="s">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="E35" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="F35" t="s">
         <v>13</v>
       </c>
       <c r="G35" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="H35" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="I35" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="J35" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="K35" t="s">
+        <v>293</v>
+      </c>
+      <c r="L35" t="s">
         <v>288</v>
       </c>
-      <c r="L35" t="s">
-        <v>283</v>
-      </c>
       <c r="M35" t="s">
-        <v>289</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="R35" t="s">
-        <v>271</v>
+        <v>295</v>
+      </c>
+      <c r="S35" t="s">
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -3405,46 +3616,46 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="B2" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C2" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="B3" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="C3" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B4" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="C4" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B5" t="s">
+        <v>303</v>
+      </c>
+      <c r="C5" t="s">
         <v>298</v>
-      </c>
-      <c r="C5" t="s">
-        <v>293</v>
       </c>
     </row>
   </sheetData>

--- a/ro-crate/ro-crate-metadata.xlsx
+++ b/ro-crate/ro-crate-metadata.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="321">
   <si>
     <t>Name</t>
   </si>
@@ -143,12 +143,12 @@
     <t>images/image-dataset-explorer.png</t>
   </si>
   <si>
+    <t>images/keyword-extractor.png</t>
+  </si>
+  <si>
     <t>images/keyword-analysis.png</t>
   </si>
   <si>
-    <t>images/keyword-extractor.png</t>
-  </si>
-  <si>
     <t>images/lameta.png</t>
   </si>
   <si>
@@ -446,6 +446,9 @@
     <t>Collocation association measures</t>
   </si>
   <si>
+    <t>"images/collocation-calculator.png"</t>
+  </si>
+  <si>
     <t>arcp://name,ConcordanceExplorer</t>
   </si>
   <si>
@@ -476,6 +479,9 @@
     <t>csv, xlsx, plain txt; also zip archive with the supported file formats</t>
   </si>
   <si>
+    <t>"images/concordancer.png"</t>
+  </si>
+  <si>
     <t>https://github.com/Australian-Text-Analytics-Platform/atap_widgets/blob/main/docs/concordance_help_pages.pdf</t>
   </si>
   <si>
@@ -503,6 +509,9 @@
     <t>Various - text, video, audio, image, etc.</t>
   </si>
   <si>
+    <t>"images/crate-o.png"</t>
+  </si>
+  <si>
     <t>https://www.ldaca.edu.au/resources/user-guides/crate-o/</t>
   </si>
   <si>
@@ -521,6 +530,9 @@
     <t>csv, xlsx</t>
   </si>
   <si>
+    <t>"images/discursis.png"</t>
+  </si>
+  <si>
     <t>https://raw.githubusercontent.com/Australian-Text-Analytics-Platform/discursis/master/docs/Discursis%20User%20Guide.pdf</t>
   </si>
   <si>
@@ -545,6 +557,9 @@
     <t>Identifies identical and similar text in a corpus</t>
   </si>
   <si>
+    <t>"images/document-similarity.png"</t>
+  </si>
+  <si>
     <t>https://github.com/Australian-Text-Analytics-Platform/document-similarity/blob/main/documents/docsim-help-pages.pdf</t>
   </si>
   <si>
@@ -620,6 +635,9 @@
     <t>Batch rename plain-text files</t>
   </si>
   <si>
+    <t>"images/file-renamer.png"</t>
+  </si>
+  <si>
     <t>arcp://name,ImageDatasetExplorer</t>
   </si>
   <si>
@@ -641,6 +659,9 @@
     <t>zip archive with jpeg and/or png files</t>
   </si>
   <si>
+    <t>"images/image-dataset-explorer.png"</t>
+  </si>
+  <si>
     <t>arcp://name,KeywordFinder</t>
   </si>
   <si>
@@ -659,6 +680,9 @@
     <t>Keyness analysis vs. a reference corpus</t>
   </si>
   <si>
+    <t>"images/keyword-extractor.png"</t>
+  </si>
+  <si>
     <t>arcp://name,KeywordsAnalysis</t>
   </si>
   <si>
@@ -669,6 +693,9 @@
   </si>
   <si>
     <t>Tool to analyse words in a collection of corpus and identify whether certain words are over or under-represented in a particular corpus compared to their representation in other corpus</t>
+  </si>
+  <si>
+    <t>"images/keyword-analysis.png"</t>
   </si>
   <si>
     <t>https://github.com/Australian-Text-Analytics-Platform/keywords-analysis/blob/main/documents/keywords_help_pages.pdf</t>
@@ -702,6 +729,9 @@
     <t>https://github.com/onset/lameta</t>
   </si>
   <si>
+    <t>"images/lameta.png"</t>
+  </si>
+  <si>
     <t>https://www.elararchive.org/uncategorized/SO_7557c4dd-1c83-485c-b95c-c0a292cfc42c/</t>
   </si>
   <si>
@@ -741,6 +771,9 @@
     <t>Part-of-speech tagging &amp; dependency parsing in 65+ languages</t>
   </si>
   <si>
+    <t>"images/pos-tagger.png"</t>
+  </si>
+  <si>
     <t>arcp://name,QuotationTool</t>
   </si>
   <si>
@@ -753,6 +786,9 @@
     <t>A tool to extract quotes and other useful information from a newspaper article/corpus</t>
   </si>
   <si>
+    <t>"images/quotation-tool.png"</t>
+  </si>
+  <si>
     <t>https://github.com/Australian-Text-Analytics-Platform/quotation-tool/blob/main/documents/quotation_help_pages.pdf</t>
   </si>
   <si>
@@ -771,6 +807,9 @@
     <t>Used to tag a text/corpus so you can extract token level semantic tags from the tagged texts</t>
   </si>
   <si>
+    <t>"images/semantic-tagger.png"</t>
+  </si>
+  <si>
     <t>https://github.com/Australian-Text-Analytics-Platform/semantic-tagger/blob/main/documents/semtag_help_pages.pdf</t>
   </si>
   <si>
@@ -792,6 +831,9 @@
     <t>Remove and replace text elements with regex</t>
   </si>
   <si>
+    <t>"images/text-cleaner.png"</t>
+  </si>
+  <si>
     <t>arcp://name,TopicExplorer</t>
   </si>
   <si>
@@ -810,6 +852,9 @@
     <t>Unsupervised &amp; seeded LDA topic modelling</t>
   </si>
   <si>
+    <t>"images/topic-detector.png"</t>
+  </si>
+  <si>
     <t>arcp://name,WordFinder</t>
   </si>
   <si>
@@ -819,6 +864,9 @@
     <t>Keyword-in-context concordancing</t>
   </si>
   <si>
+    <t>"images/word-finder.png"</t>
+  </si>
+  <si>
     <t>arcp://name,WordWebber</t>
   </si>
   <si>
@@ -826,6 +874,9 @@
   </si>
   <si>
     <t>Word co-occurrence network visualisation</t>
+  </si>
+  <si>
+    <t>"images/word-webber.png"</t>
   </si>
   <si>
     <t>https://data.ldaca.edu.au/object?_id=https://github.com/Australian-Text-Analytics-Platform/cooee/blob/main/cooee.ipynb</t>
@@ -2246,12 +2297,12 @@
         <v>136</v>
       </c>
       <c r="N4" t="s">
-        <v>32</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B5" t="s">
         <v>120</v>
@@ -2263,7 +2314,7 @@
         <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
@@ -2281,7 +2332,7 @@
         <v>134</v>
       </c>
       <c r="K5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L5" t="s">
         <v>136</v>
@@ -2289,7 +2340,7 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B6" t="s">
         <v>120</v>
@@ -2301,45 +2352,45 @@
         <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I6" t="s">
         <v>125</v>
       </c>
       <c r="J6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K6" t="s">
+        <v>151</v>
+      </c>
+      <c r="L6" t="s">
+        <v>152</v>
+      </c>
+      <c r="M6" t="s">
         <v>150</v>
       </c>
-      <c r="L6" t="s">
-        <v>151</v>
-      </c>
-      <c r="M6" t="s">
-        <v>149</v>
-      </c>
       <c r="N6" t="s">
-        <v>35</v>
+        <v>153</v>
       </c>
       <c r="O6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="P6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B7" t="s">
         <v>120</v>
@@ -2351,42 +2402,42 @@
         <v>34</v>
       </c>
       <c r="E7" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F7" t="s">
         <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H7" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I7" t="s">
         <v>139</v>
       </c>
       <c r="J7" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="K7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="L7" t="s">
+        <v>162</v>
+      </c>
+      <c r="M7" t="s">
         <v>160</v>
       </c>
-      <c r="M7" t="s">
-        <v>158</v>
-      </c>
       <c r="N7" t="s">
-        <v>36</v>
+        <v>163</v>
       </c>
       <c r="O7" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B8" t="s">
         <v>120</v>
@@ -2398,45 +2449,45 @@
         <v>34</v>
       </c>
       <c r="E8" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I8" t="s">
         <v>125</v>
       </c>
       <c r="J8" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="K8" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="L8" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M8" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="N8" t="s">
-        <v>37</v>
+        <v>170</v>
       </c>
       <c r="O8" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="P8" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="Q8" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B9" t="s">
         <v>120</v>
@@ -2448,45 +2499,45 @@
         <v>34</v>
       </c>
       <c r="E9" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="F9" t="s">
         <v>13</v>
       </c>
       <c r="G9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H9" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="I9" t="s">
         <v>125</v>
       </c>
       <c r="J9" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="K9" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="L9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M9" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="N9" t="s">
-        <v>38</v>
+        <v>179</v>
       </c>
       <c r="O9" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="P9" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="B10" t="s">
         <v>120</v>
@@ -2498,7 +2549,7 @@
         <v>34</v>
       </c>
       <c r="E10" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="F10" t="s">
         <v>13</v>
@@ -2510,24 +2561,24 @@
         <v>124</v>
       </c>
       <c r="I10" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="J10" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="K10" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="L10" t="s">
         <v>128</v>
       </c>
       <c r="M10" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B11" t="s">
         <v>120</v>
@@ -2539,7 +2590,7 @@
         <v>34</v>
       </c>
       <c r="E11" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
@@ -2551,24 +2602,24 @@
         <v>124</v>
       </c>
       <c r="I11" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="J11" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="K11" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="L11" t="s">
+        <v>190</v>
+      </c>
+      <c r="M11" t="s">
         <v>185</v>
-      </c>
-      <c r="M11" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B12" t="s">
         <v>120</v>
@@ -2580,7 +2631,7 @@
         <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
@@ -2595,10 +2646,10 @@
         <v>139</v>
       </c>
       <c r="J12" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="K12" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="L12" t="s">
         <v>128</v>
@@ -2606,7 +2657,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B13" t="s">
         <v>120</v>
@@ -2618,7 +2669,7 @@
         <v>34</v>
       </c>
       <c r="E13" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="F13" t="s">
         <v>13</v>
@@ -2633,10 +2684,10 @@
         <v>139</v>
       </c>
       <c r="J13" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="K13" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="L13" t="s">
         <v>128</v>
@@ -2644,7 +2695,7 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B14" t="s">
         <v>120</v>
@@ -2656,7 +2707,7 @@
         <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
@@ -2668,24 +2719,24 @@
         <v>124</v>
       </c>
       <c r="I14" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="J14" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="K14" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="L14" t="s">
         <v>128</v>
       </c>
       <c r="M14" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B15" t="s">
         <v>120</v>
@@ -2697,7 +2748,7 @@
         <v>34</v>
       </c>
       <c r="E15" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
@@ -2715,18 +2766,18 @@
         <v>140</v>
       </c>
       <c r="K15" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="L15" t="s">
         <v>136</v>
       </c>
       <c r="N15" t="s">
-        <v>39</v>
+        <v>205</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B16" t="s">
         <v>120</v>
@@ -2738,39 +2789,39 @@
         <v>34</v>
       </c>
       <c r="E16" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="H16" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="I16" t="s">
         <v>125</v>
       </c>
       <c r="J16" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="K16" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="L16" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="M16" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="N16" t="s">
-        <v>40</v>
+        <v>213</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="B17" t="s">
         <v>120</v>
@@ -2782,7 +2833,7 @@
         <v>34</v>
       </c>
       <c r="E17" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="F17" t="s">
         <v>13</v>
@@ -2800,7 +2851,7 @@
         <v>134</v>
       </c>
       <c r="K17" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="L17" t="s">
         <v>136</v>
@@ -2808,7 +2859,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B18" t="s">
         <v>120</v>
@@ -2820,7 +2871,7 @@
         <v>34</v>
       </c>
       <c r="E18" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="F18" t="s">
         <v>13</v>
@@ -2838,18 +2889,18 @@
         <v>140</v>
       </c>
       <c r="K18" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="L18" t="s">
         <v>136</v>
       </c>
       <c r="N18" t="s">
-        <v>42</v>
+        <v>220</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B19" t="s">
         <v>120</v>
@@ -2861,45 +2912,45 @@
         <v>34</v>
       </c>
       <c r="E19" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="F19" t="s">
         <v>13</v>
       </c>
       <c r="G19" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H19" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="I19" t="s">
         <v>125</v>
       </c>
       <c r="J19" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="K19" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="L19" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M19" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="N19" t="s">
-        <v>41</v>
+        <v>225</v>
       </c>
       <c r="O19" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="P19" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s">
         <v>120</v>
@@ -2911,45 +2962,45 @@
         <v>34</v>
       </c>
       <c r="E20" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="F20" t="s">
         <v>13</v>
       </c>
       <c r="G20" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="H20" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="I20" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="J20" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="K20" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="L20" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="M20" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="N20" t="s">
-        <v>43</v>
+        <v>236</v>
       </c>
       <c r="O20" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="P20" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="B21" t="s">
         <v>120</v>
@@ -2961,7 +3012,7 @@
         <v>34</v>
       </c>
       <c r="E21" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="F21" t="s">
         <v>13</v>
@@ -2979,18 +3030,18 @@
         <v>134</v>
       </c>
       <c r="K21" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="L21" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="Q21" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="B22" t="s">
         <v>120</v>
@@ -3002,7 +3053,7 @@
         <v>34</v>
       </c>
       <c r="E22" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="F22" t="s">
         <v>13</v>
@@ -3020,7 +3071,7 @@
         <v>134</v>
       </c>
       <c r="K22" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="L22" t="s">
         <v>136</v>
@@ -3028,7 +3079,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="B23" t="s">
         <v>120</v>
@@ -3040,7 +3091,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F23" t="s">
         <v>13</v>
@@ -3058,18 +3109,18 @@
         <v>140</v>
       </c>
       <c r="K23" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="L23" t="s">
         <v>136</v>
       </c>
       <c r="N23" t="s">
-        <v>44</v>
+        <v>250</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="B24" t="s">
         <v>120</v>
@@ -3081,45 +3132,45 @@
         <v>34</v>
       </c>
       <c r="E24" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="F24" t="s">
         <v>13</v>
       </c>
       <c r="G24" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H24" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="I24" t="s">
         <v>125</v>
       </c>
       <c r="J24" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="K24" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="L24" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M24" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="N24" t="s">
-        <v>45</v>
+        <v>255</v>
       </c>
       <c r="O24" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="P24" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="B25" t="s">
         <v>120</v>
@@ -3131,45 +3182,45 @@
         <v>34</v>
       </c>
       <c r="E25" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="F25" t="s">
         <v>13</v>
       </c>
       <c r="G25" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H25" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="I25" t="s">
         <v>125</v>
       </c>
       <c r="J25" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="K25" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="L25" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M25" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="N25" t="s">
-        <v>46</v>
+        <v>262</v>
       </c>
       <c r="O25" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="P25" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="B26" t="s">
         <v>120</v>
@@ -3181,7 +3232,7 @@
         <v>34</v>
       </c>
       <c r="E26" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="F26" t="s">
         <v>13</v>
@@ -3199,7 +3250,7 @@
         <v>140</v>
       </c>
       <c r="K26" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="L26" t="s">
         <v>136</v>
@@ -3207,7 +3258,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="B27" t="s">
         <v>120</v>
@@ -3219,7 +3270,7 @@
         <v>34</v>
       </c>
       <c r="E27" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="F27" t="s">
         <v>13</v>
@@ -3237,18 +3288,18 @@
         <v>140</v>
       </c>
       <c r="K27" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="L27" t="s">
         <v>136</v>
       </c>
       <c r="N27" t="s">
-        <v>48</v>
+        <v>270</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="B28" t="s">
         <v>120</v>
@@ -3260,7 +3311,7 @@
         <v>34</v>
       </c>
       <c r="E28" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="F28" t="s">
         <v>13</v>
@@ -3278,7 +3329,7 @@
         <v>134</v>
       </c>
       <c r="K28" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="L28" t="s">
         <v>136</v>
@@ -3286,7 +3337,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="B29" t="s">
         <v>120</v>
@@ -3298,7 +3349,7 @@
         <v>34</v>
       </c>
       <c r="E29" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="F29" t="s">
         <v>13</v>
@@ -3316,18 +3367,18 @@
         <v>140</v>
       </c>
       <c r="K29" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="L29" t="s">
         <v>136</v>
       </c>
       <c r="N29" t="s">
-        <v>49</v>
+        <v>277</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="B30" t="s">
         <v>120</v>
@@ -3339,7 +3390,7 @@
         <v>34</v>
       </c>
       <c r="E30" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="F30" t="s">
         <v>13</v>
@@ -3357,18 +3408,18 @@
         <v>140</v>
       </c>
       <c r="K30" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="L30" t="s">
         <v>136</v>
       </c>
       <c r="N30" t="s">
-        <v>50</v>
+        <v>281</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="B31" t="s">
         <v>120</v>
@@ -3380,7 +3431,7 @@
         <v>34</v>
       </c>
       <c r="E31" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="F31" t="s">
         <v>13</v>
@@ -3398,33 +3449,33 @@
         <v>140</v>
       </c>
       <c r="K31" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="L31" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="N31" t="s">
-        <v>51</v>
+        <v>285</v>
       </c>
       <c r="Q31" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s">
         <v>120</v>
       </c>
       <c r="C32" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="D32" t="s">
         <v>34</v>
       </c>
       <c r="E32" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="F32" t="s">
         <v>13</v>
@@ -3433,160 +3484,160 @@
         <v>123</v>
       </c>
       <c r="H32" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="I32" t="s">
         <v>125</v>
       </c>
       <c r="J32" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="K32" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="M32" t="s">
-        <v>274</v>
+        <v>291</v>
       </c>
       <c r="R32" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="S32" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="B33" t="s">
         <v>120</v>
       </c>
       <c r="C33" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="D33" t="s">
         <v>34</v>
       </c>
       <c r="E33" t="s">
-        <v>278</v>
+        <v>295</v>
       </c>
       <c r="F33" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="G33" t="s">
         <v>123</v>
       </c>
       <c r="H33" t="s">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="I33" t="s">
         <v>125</v>
       </c>
       <c r="J33" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="L33" t="s">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="M33" t="s">
-        <v>277</v>
+        <v>294</v>
       </c>
       <c r="R33" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="S33" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="B34" t="s">
         <v>120</v>
       </c>
       <c r="C34" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="D34" t="s">
         <v>34</v>
       </c>
       <c r="E34" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="G34" t="s">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="H34" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="I34" t="s">
         <v>125</v>
       </c>
       <c r="J34" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="K34" t="s">
-        <v>287</v>
+        <v>304</v>
       </c>
       <c r="L34" t="s">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="M34" t="s">
-        <v>289</v>
+        <v>306</v>
       </c>
       <c r="R34" t="s">
-        <v>290</v>
+        <v>307</v>
       </c>
       <c r="S34" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="B35" t="s">
         <v>120</v>
       </c>
       <c r="C35" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
       <c r="D35" t="s">
         <v>34</v>
       </c>
       <c r="E35" t="s">
-        <v>292</v>
+        <v>309</v>
       </c>
       <c r="F35" t="s">
         <v>13</v>
       </c>
       <c r="G35" t="s">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="H35" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
       <c r="I35" t="s">
         <v>125</v>
       </c>
       <c r="J35" t="s">
-        <v>291</v>
+        <v>308</v>
       </c>
       <c r="K35" t="s">
+        <v>310</v>
+      </c>
+      <c r="L35" t="s">
+        <v>305</v>
+      </c>
+      <c r="M35" t="s">
+        <v>311</v>
+      </c>
+      <c r="R35" t="s">
+        <v>312</v>
+      </c>
+      <c r="S35" t="s">
         <v>293</v>
-      </c>
-      <c r="L35" t="s">
-        <v>288</v>
-      </c>
-      <c r="M35" t="s">
-        <v>294</v>
-      </c>
-      <c r="R35" t="s">
-        <v>295</v>
-      </c>
-      <c r="S35" t="s">
-        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -3616,46 +3667,46 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="B2" t="s">
-        <v>297</v>
+        <v>314</v>
       </c>
       <c r="C2" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>299</v>
+        <v>316</v>
       </c>
       <c r="B3" t="s">
-        <v>300</v>
+        <v>317</v>
       </c>
       <c r="C3" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>301</v>
+        <v>318</v>
       </c>
       <c r="B4" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="C4" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>302</v>
+        <v>319</v>
       </c>
       <c r="B5" t="s">
-        <v>303</v>
+        <v>320</v>
       </c>
       <c r="C5" t="s">
-        <v>298</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>

--- a/ro-crate/ro-crate-metadata.xlsx
+++ b/ro-crate/ro-crate-metadata.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="328">
   <si>
     <t>Name</t>
   </si>
@@ -92,7 +92,7 @@
     <t>pcdm:hasMember</t>
   </si>
   <si>
-    <t>["arcp://name,AnonymisingELANFiles", "arcp://name,CollocationAnalyser", "arcp://name,CollocationCalculator", "arcp://name,ConcordanceExplorer", "arcp://name,Concordancer", "arcp://name,Crate-O", "arcp://name,Discursis", "arcp://name,DocumentSimilarity", "arcp://name,ELANAnnotationSplitter", "arcp://name,ELANAudioSegmentation", "arcp://name,ELANCommander", "arcp://name,ELANInventory", "arcp://name,ELANReplacer", "arcp://name,FileRenamer", "arcp://name,ImageDatasetExplorer", "arcp://name,KeywordFinder", "arcp://name,KeywordExtractor", "arcp://name,KeywordsAnalysis", "arcp://name,Lameta", "arcp://name,NetworkVisualiser", "arcp://name,Part-of-SpeechTagger", "arcp://name,POSTagger", "arcp://name,QuotationTool", "arcp://name,SemanticTaggerEnglish", "arcp://name,SentimentExplorer", "arcp://name,TextCleaner", "arcp://name,TopicExplorer", "arcp://name,TopicDetector", "arcp://name,WordFinder", "arcp://name,WordWebber", "https://data.ldaca.edu.au/object?_id=https://github.com/Australian-Text-Analytics-Platform/cooee/blob/main/cooee.ipynb", "https://github.com/Australian-Text-Analytics-Platform/farms-to-freeways", "https://data.ldaca.edu.au/object?_id=https%3A%2F%2Fgithub.com%2FAustralian-Text-Analytics-Platform%2Fnotebook-ausreddit%2Fblob%2Fmain%2Fexploration.ipynb", "https://data.ldaca.edu.au/object?_id=https%3A%2F%2Fgithub.com%2FAustralian-Text-Analytics-Platform%2Fnotebook-twittersphere%2Fblob%2Fmain%2Fexploration.ipynb"]</t>
+    <t>["arcp://name,AnonymisingELANFiles", "arcp://name,CollocationAnalyser", "arcp://name,CollocationCalculator", "arcp://name,ConcordanceExplorer", "arcp://name,Concordancer", "arcp://name,Crate-O", "arcp://name,Discursis", "arcp://name,DocumentSimilarity", "arcp://name,ELANAnnotationSplitter", "arcp://name,ELANAudioSegmentation", "arcp://name,ELANCommander", "arcp://name,ELANInventory", "arcp://name,ELANReplacer", "arcp://name,FileRenamer", "arcp://name,ImageDatasetExplorer", "arcp://name,KeywordFinder", "arcp://name,KeywordExtractor", "arcp://name,KeywordsAnalysis", "arcp://name,Lameta", "arcp://name,NetworkVisualiser", "arcp://name,Part-of-SpeechTagger", "arcp://name,POSTagger", "arcp://name,QuotationTool", "arcp://name,SemanticTaggerEnglish", "arcp://name,SentimentExplorer", "arcp://name,SentimentExplorerbrowser-based", "arcp://name,TextCleaner", "arcp://name,TextCleanerbrowser-based", "arcp://name,TopicExplorer", "arcp://name,TopicDetector", "arcp://name,WordFinder", "arcp://name,WordWebber", "https://data.ldaca.edu.au/object?_id=https://github.com/Australian-Text-Analytics-Platform/cooee/blob/main/cooee.ipynb", "https://github.com/Australian-Text-Analytics-Platform/farms-to-freeways", "https://data.ldaca.edu.au/object?_id=https%3A%2F%2Fgithub.com%2FAustralian-Text-Analytics-Platform%2Fnotebook-ausreddit%2Fblob%2Fmain%2Fexploration.ipynb", "https://data.ldaca.edu.au/object?_id=https%3A%2F%2Fgithub.com%2FAustralian-Text-Analytics-Platform%2Fnotebook-twittersphere%2Fblob%2Fmain%2Fexploration.ipynb"]</t>
   </si>
   <si>
     <t>hasPart</t>
@@ -816,16 +816,37 @@
     <t>arcp://name,SentimentExplorer</t>
   </si>
   <si>
-    <t>SentimentExplorer</t>
+    <t>Sentiment Explorer</t>
+  </si>
+  <si>
+    <t>Allows you to perform a sentiment analysis on your texts and download the results in an MS Excel spreadsheet.</t>
+  </si>
+  <si>
+    <t>arcp://name,SentimentExplorerbrowser-based</t>
+  </si>
+  <si>
+    <t>Sentiment Explorer (browser-based)</t>
   </si>
   <si>
     <t>NRC word-emotion sentiment analysis</t>
   </si>
   <si>
+    <t>"images/sentiment-explorer.png"</t>
+  </si>
+  <si>
     <t>arcp://name,TextCleaner</t>
   </si>
   <si>
-    <t>TextCleaner</t>
+    <t>Text Cleaner</t>
+  </si>
+  <si>
+    <t>Allows you to remove and replace words, tags, and other elements from the text data that you upload (of course you can then download the cleaned texts too)</t>
+  </si>
+  <si>
+    <t>arcp://name,TextCleanerbrowser-based</t>
+  </si>
+  <si>
+    <t>TextCleaner (browser-based)</t>
   </si>
   <si>
     <t>Remove and replace text elements with regex</t>
@@ -2115,7 +2136,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S35"/>
+  <dimension ref="A1:S37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="19" width="20" customWidth="1"/>
@@ -3244,10 +3265,10 @@
         <v>132</v>
       </c>
       <c r="I26" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="J26" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="K26" t="s">
         <v>266</v>
@@ -3376,7 +3397,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>278</v>
       </c>
@@ -3402,10 +3423,10 @@
         <v>132</v>
       </c>
       <c r="I30" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="J30" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="K30" t="s">
         <v>280</v>
@@ -3413,13 +3434,10 @@
       <c r="L30" t="s">
         <v>136</v>
       </c>
-      <c r="N30" t="s">
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>281</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>282</v>
       </c>
       <c r="B31" t="s">
         <v>120</v>
@@ -3431,7 +3449,7 @@
         <v>34</v>
       </c>
       <c r="E31" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F31" t="s">
         <v>13</v>
@@ -3449,195 +3467,277 @@
         <v>140</v>
       </c>
       <c r="K31" t="s">
+        <v>283</v>
+      </c>
+      <c r="L31" t="s">
+        <v>136</v>
+      </c>
+      <c r="N31" t="s">
         <v>284</v>
       </c>
-      <c r="L31" t="s">
-        <v>242</v>
-      </c>
-      <c r="N31" t="s">
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>285</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>286</v>
       </c>
       <c r="B32" t="s">
         <v>120</v>
       </c>
       <c r="C32" t="s">
-        <v>287</v>
+        <v>121</v>
       </c>
       <c r="D32" t="s">
         <v>34</v>
       </c>
       <c r="E32" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F32" t="s">
         <v>13</v>
       </c>
       <c r="G32" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="H32" t="s">
+        <v>132</v>
+      </c>
+      <c r="I32" t="s">
+        <v>139</v>
+      </c>
+      <c r="J32" t="s">
+        <v>140</v>
+      </c>
+      <c r="K32" t="s">
+        <v>287</v>
+      </c>
+      <c r="L32" t="s">
+        <v>136</v>
+      </c>
+      <c r="N32" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>289</v>
-      </c>
-      <c r="I32" t="s">
-        <v>125</v>
-      </c>
-      <c r="J32" t="s">
-        <v>286</v>
-      </c>
-      <c r="K32" t="s">
-        <v>290</v>
-      </c>
-      <c r="M32" t="s">
-        <v>291</v>
-      </c>
-      <c r="R32" t="s">
-        <v>292</v>
-      </c>
-      <c r="S32" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>294</v>
       </c>
       <c r="B33" t="s">
         <v>120</v>
       </c>
       <c r="C33" t="s">
-        <v>287</v>
+        <v>121</v>
       </c>
       <c r="D33" t="s">
         <v>34</v>
       </c>
       <c r="E33" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="F33" t="s">
-        <v>296</v>
+        <v>13</v>
       </c>
       <c r="G33" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="H33" t="s">
-        <v>297</v>
+        <v>132</v>
       </c>
       <c r="I33" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="J33" t="s">
-        <v>294</v>
+        <v>140</v>
+      </c>
+      <c r="K33" t="s">
+        <v>291</v>
       </c>
       <c r="L33" t="s">
-        <v>298</v>
-      </c>
-      <c r="M33" t="s">
-        <v>294</v>
-      </c>
-      <c r="R33" t="s">
-        <v>299</v>
-      </c>
-      <c r="S33" t="s">
-        <v>293</v>
+        <v>242</v>
+      </c>
+      <c r="N33" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="B34" t="s">
         <v>120</v>
       </c>
       <c r="C34" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="D34" t="s">
         <v>34</v>
       </c>
       <c r="E34" t="s">
-        <v>301</v>
+        <v>295</v>
+      </c>
+      <c r="F34" t="s">
+        <v>13</v>
       </c>
       <c r="G34" t="s">
-        <v>302</v>
+        <v>123</v>
       </c>
       <c r="H34" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="I34" t="s">
         <v>125</v>
       </c>
       <c r="J34" t="s">
+        <v>293</v>
+      </c>
+      <c r="K34" t="s">
+        <v>297</v>
+      </c>
+      <c r="M34" t="s">
+        <v>298</v>
+      </c>
+      <c r="R34" t="s">
+        <v>299</v>
+      </c>
+      <c r="S34" t="s">
         <v>300</v>
-      </c>
-      <c r="K34" t="s">
-        <v>304</v>
-      </c>
-      <c r="L34" t="s">
-        <v>305</v>
-      </c>
-      <c r="M34" t="s">
-        <v>306</v>
-      </c>
-      <c r="R34" t="s">
-        <v>307</v>
-      </c>
-      <c r="S34" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="B35" t="s">
         <v>120</v>
       </c>
       <c r="C35" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="D35" t="s">
         <v>34</v>
       </c>
       <c r="E35" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="F35" t="s">
-        <v>13</v>
+        <v>303</v>
       </c>
       <c r="G35" t="s">
-        <v>302</v>
+        <v>123</v>
       </c>
       <c r="H35" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="I35" t="s">
         <v>125</v>
       </c>
       <c r="J35" t="s">
-        <v>308</v>
-      </c>
-      <c r="K35" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="L35" t="s">
         <v>305</v>
       </c>
       <c r="M35" t="s">
+        <v>301</v>
+      </c>
+      <c r="R35" t="s">
+        <v>306</v>
+      </c>
+      <c r="S35" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>307</v>
+      </c>
+      <c r="B36" t="s">
+        <v>120</v>
+      </c>
+      <c r="C36" t="s">
+        <v>294</v>
+      </c>
+      <c r="D36" t="s">
+        <v>34</v>
+      </c>
+      <c r="E36" t="s">
+        <v>308</v>
+      </c>
+      <c r="G36" t="s">
+        <v>309</v>
+      </c>
+      <c r="H36" t="s">
+        <v>310</v>
+      </c>
+      <c r="I36" t="s">
+        <v>125</v>
+      </c>
+      <c r="J36" t="s">
+        <v>307</v>
+      </c>
+      <c r="K36" t="s">
         <v>311</v>
       </c>
-      <c r="R35" t="s">
+      <c r="L36" t="s">
         <v>312</v>
       </c>
-      <c r="S35" t="s">
-        <v>293</v>
+      <c r="M36" t="s">
+        <v>313</v>
+      </c>
+      <c r="R36" t="s">
+        <v>314</v>
+      </c>
+      <c r="S36" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>315</v>
+      </c>
+      <c r="B37" t="s">
+        <v>120</v>
+      </c>
+      <c r="C37" t="s">
+        <v>294</v>
+      </c>
+      <c r="D37" t="s">
+        <v>34</v>
+      </c>
+      <c r="E37" t="s">
+        <v>316</v>
+      </c>
+      <c r="F37" t="s">
+        <v>13</v>
+      </c>
+      <c r="G37" t="s">
+        <v>309</v>
+      </c>
+      <c r="H37" t="s">
+        <v>310</v>
+      </c>
+      <c r="I37" t="s">
+        <v>125</v>
+      </c>
+      <c r="J37" t="s">
+        <v>315</v>
+      </c>
+      <c r="K37" t="s">
+        <v>317</v>
+      </c>
+      <c r="L37" t="s">
+        <v>312</v>
+      </c>
+      <c r="M37" t="s">
+        <v>318</v>
+      </c>
+      <c r="R37" t="s">
+        <v>319</v>
+      </c>
+      <c r="S37" t="s">
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -3667,46 +3767,46 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="B2" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="C2" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="B3" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="C3" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="B4" t="s">
         <v>238</v>
       </c>
       <c r="C4" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="B5" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="C5" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>
